--- a/UAT _test_proje_01.xlsx
+++ b/UAT _test_proje_01.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intel\Desktop\Sales_Profit_Analysis_Dashboard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABC6611-81F1-4F44-886E-2CE393FD2637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="UAT_Test_Case" sheetId="1" r:id="rId5"/>
+    <sheet name="UAT_Test_Case" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -314,7 +336,7 @@
   </si>
   <si>
     <t xml:space="preserve">UAT Status: APPROVED
-Validated By: Aspiring Business Analyst - Aaditya
+Validated By: Mohit Sharma
 Validation Date: 10/02/2026
 Remarks: Dashboard validated and ready for production use
 </t>
@@ -323,21 +345,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -345,6 +369,7 @@
     <font>
       <b/>
       <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -355,7 +380,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -413,148 +438,115 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="4" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFBDBDBD"/>
           <bgColor rgb="FFBDBDBD"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="UAT_Test_Case-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="UAT_Test_Case-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="M5" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="M5" headerRowCount="0">
   <tableColumns count="1">
-    <tableColumn name="Column1" id="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
   </tableColumns>
-  <tableStyleInfo name="UAT_Test_Case-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="UAT_Test_Case-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
@@ -564,7 +556,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -754,17 +746,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,7 +811,7 @@
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="3"/>
       <c r="C2" s="5"/>
@@ -852,35 +847,35 @@
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6"/>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="7"/>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="J3" s="8"/>
-      <c r="K3" s="15">
-        <v>9994.0</v>
+      <c r="K3" s="9">
+        <v>9994</v>
       </c>
       <c r="L3" s="9"/>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O3" s="3"/>
@@ -904,7 +899,7 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="3"/>
       <c r="C4" s="5"/>
@@ -940,35 +935,35 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="6"/>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="7"/>
-      <c r="I5" s="18">
+      <c r="I5" s="11">
         <v>2297200.86</v>
       </c>
       <c r="J5" s="8"/>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="9"/>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="N5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O5" s="3"/>
@@ -992,7 +987,7 @@
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="3"/>
       <c r="C6" s="5"/>
@@ -1028,35 +1023,35 @@
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="6"/>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="7"/>
-      <c r="I7" s="18">
+      <c r="I7" s="11">
         <v>286397.02</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="9"/>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="3"/>
@@ -1080,7 +1075,7 @@
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="3"/>
       <c r="C8" s="5"/>
@@ -1116,35 +1111,35 @@
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="6"/>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H9" s="7"/>
-      <c r="I9" s="19">
-        <v>0.1247</v>
+      <c r="I9" s="12">
+        <v>0.12470000000000001</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="20">
-        <v>0.1247</v>
+      <c r="K9" s="13">
+        <v>0.12470000000000001</v>
       </c>
       <c r="L9" s="9"/>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O9" s="3"/>
@@ -1168,7 +1163,7 @@
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="3"/>
       <c r="C10" s="5"/>
@@ -1204,35 +1199,35 @@
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="6"/>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="7" t="s">
         <v>32</v>
       </c>
       <c r="H11" s="7"/>
-      <c r="I11" s="14">
-        <v>1871.0</v>
+      <c r="I11" s="8">
+        <v>1871</v>
       </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="L11" s="9"/>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O11" s="3"/>
@@ -1256,7 +1251,7 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="3"/>
       <c r="C12" s="5"/>
@@ -1292,35 +1287,35 @@
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="6" t="s">
         <v>36</v>
       </c>
       <c r="F13" s="6"/>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="7"/>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="8" t="s">
         <v>38</v>
       </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="9" t="s">
         <v>38</v>
       </c>
       <c r="L13" s="9"/>
-      <c r="M13" s="16" t="s">
+      <c r="M13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O13" s="3"/>
@@ -1344,7 +1339,7 @@
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="3"/>
       <c r="C14" s="5"/>
@@ -1380,35 +1375,35 @@
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F15" s="6"/>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="7" t="s">
         <v>42</v>
       </c>
       <c r="H15" s="7"/>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="8" t="s">
         <v>43</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="9" t="s">
         <v>44</v>
       </c>
       <c r="L15" s="9"/>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O15" s="3"/>
@@ -1432,7 +1427,7 @@
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="3"/>
       <c r="C16" s="5"/>
@@ -1468,35 +1463,35 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="6"/>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H17" s="7"/>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="8" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="8"/>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="9" t="s">
         <v>50</v>
       </c>
       <c r="L17" s="9"/>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N17" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O17" s="3"/>
@@ -1520,7 +1515,7 @@
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="3"/>
       <c r="C18" s="5"/>
@@ -1556,35 +1551,35 @@
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="6" t="s">
         <v>53</v>
       </c>
       <c r="F19" s="6"/>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="7" t="s">
         <v>54</v>
       </c>
       <c r="H19" s="7"/>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="8" t="s">
         <v>55</v>
       </c>
       <c r="J19" s="8"/>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="9" t="s">
         <v>56</v>
       </c>
       <c r="L19" s="9"/>
-      <c r="M19" s="16" t="s">
+      <c r="M19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N19" s="14" t="s">
+      <c r="N19" s="8" t="s">
         <v>57</v>
       </c>
       <c r="O19" s="3"/>
@@ -1608,7 +1603,7 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="3"/>
       <c r="C20" s="5"/>
@@ -1644,35 +1639,35 @@
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="6" t="s">
         <v>60</v>
       </c>
       <c r="F21" s="6"/>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="7" t="s">
         <v>61</v>
       </c>
       <c r="H21" s="7"/>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="8" t="s">
         <v>62</v>
       </c>
       <c r="J21" s="8"/>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="9" t="s">
         <v>63</v>
       </c>
       <c r="L21" s="9"/>
-      <c r="M21" s="16" t="s">
+      <c r="M21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N21" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O21" s="3"/>
@@ -1696,7 +1691,7 @@
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="3"/>
       <c r="C22" s="5"/>
@@ -1732,35 +1727,35 @@
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="6" t="s">
         <v>66</v>
       </c>
       <c r="F23" s="6"/>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="7" t="s">
         <v>67</v>
       </c>
       <c r="H23" s="7"/>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="8" t="s">
         <v>68</v>
       </c>
       <c r="J23" s="8"/>
-      <c r="K23" s="15" t="s">
+      <c r="K23" s="9" t="s">
         <v>69</v>
       </c>
       <c r="L23" s="9"/>
-      <c r="M23" s="16" t="s">
+      <c r="M23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O23" s="3"/>
@@ -1784,7 +1779,7 @@
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="3"/>
       <c r="C24" s="5"/>
@@ -1820,35 +1815,35 @@
       <c r="AG24" s="3"/>
       <c r="AH24" s="3"/>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="s">
+    <row r="25" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D25" s="5"/>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="6" t="s">
         <v>72</v>
       </c>
       <c r="F25" s="6"/>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="7" t="s">
         <v>73</v>
       </c>
       <c r="H25" s="7"/>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="8" t="s">
         <v>74</v>
       </c>
       <c r="J25" s="8"/>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="9" t="s">
         <v>74</v>
       </c>
       <c r="L25" s="9"/>
-      <c r="M25" s="16" t="s">
+      <c r="M25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N25" s="17" t="s">
+      <c r="N25" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O25" s="3"/>
@@ -1872,7 +1867,7 @@
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="3"/>
       <c r="C26" s="5"/>
@@ -1908,35 +1903,35 @@
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="6" t="s">
         <v>77</v>
       </c>
       <c r="F27" s="6"/>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="7" t="s">
         <v>78</v>
       </c>
       <c r="H27" s="7"/>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="8" t="s">
         <v>79</v>
       </c>
       <c r="J27" s="8"/>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="L27" s="9"/>
-      <c r="M27" s="16" t="s">
+      <c r="M27" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N27" s="17" t="s">
+      <c r="N27" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O27" s="3"/>
@@ -1960,7 +1955,7 @@
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="3"/>
       <c r="C28" s="5"/>
@@ -1996,35 +1991,35 @@
       <c r="AG28" s="3"/>
       <c r="AH28" s="3"/>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="6" t="s">
         <v>83</v>
       </c>
       <c r="F29" s="6"/>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="7" t="s">
         <v>84</v>
       </c>
       <c r="H29" s="7"/>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="8" t="s">
         <v>85</v>
       </c>
       <c r="J29" s="8"/>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="9" t="s">
         <v>86</v>
       </c>
       <c r="L29" s="9"/>
-      <c r="M29" s="16" t="s">
+      <c r="M29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N29" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O29" s="3"/>
@@ -2048,7 +2043,7 @@
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="3"/>
       <c r="C30" s="5"/>
@@ -2084,35 +2079,35 @@
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="s">
+    <row r="31" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="5" t="s">
         <v>88</v>
       </c>
       <c r="D31" s="5"/>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="6" t="s">
         <v>89</v>
       </c>
       <c r="F31" s="6"/>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="7" t="s">
         <v>90</v>
       </c>
       <c r="H31" s="7"/>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="8" t="s">
         <v>91</v>
       </c>
       <c r="J31" s="8"/>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="9" t="s">
         <v>92</v>
       </c>
       <c r="L31" s="9"/>
-      <c r="M31" s="16" t="s">
+      <c r="M31" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N31" s="17" t="s">
+      <c r="N31" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O31" s="3"/>
@@ -2136,7 +2131,7 @@
       <c r="AG31" s="3"/>
       <c r="AH31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="3"/>
       <c r="C32" s="5"/>
@@ -2172,35 +2167,35 @@
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="5" t="s">
         <v>94</v>
       </c>
       <c r="D33" s="5"/>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="6" t="s">
         <v>95</v>
       </c>
       <c r="F33" s="6"/>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="7" t="s">
         <v>96</v>
       </c>
       <c r="H33" s="7"/>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="8" t="s">
         <v>97</v>
       </c>
       <c r="J33" s="8"/>
-      <c r="K33" s="15" t="s">
+      <c r="K33" s="9" t="s">
         <v>98</v>
       </c>
       <c r="L33" s="9"/>
-      <c r="M33" s="16" t="s">
+      <c r="M33" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" s="8" t="s">
         <v>99</v>
       </c>
       <c r="O33" s="3"/>
@@ -2224,7 +2219,7 @@
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2260,7 +2255,7 @@
       <c r="AG34" s="3"/>
       <c r="AH34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2296,7 +2291,7 @@
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2332,7 +2327,7 @@
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2368,18 +2363,18 @@
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="s">
+    <row r="38" spans="1:34" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -2406,7 +2401,7 @@
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2442,7 +2437,7 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2478,7 +2473,7 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2514,7 +2509,7 @@
       <c r="AG41" s="3"/>
       <c r="AH41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2550,7 +2545,7 @@
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2586,7 +2581,7 @@
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2622,7 +2617,7 @@
       <c r="AG44" s="3"/>
       <c r="AH44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2658,7 +2653,7 @@
       <c r="AG45" s="3"/>
       <c r="AH45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2694,7 +2689,7 @@
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2730,7 +2725,7 @@
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2766,7 +2761,7 @@
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2802,7 +2797,7 @@
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2838,7 +2833,7 @@
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2874,7 +2869,7 @@
       <c r="AG51" s="3"/>
       <c r="AH51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2910,7 +2905,7 @@
       <c r="AG52" s="3"/>
       <c r="AH52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2946,7 +2941,7 @@
       <c r="AG53" s="3"/>
       <c r="AH53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2982,7 +2977,7 @@
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3018,7 +3013,7 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3054,7 +3049,7 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3090,7 +3085,7 @@
       <c r="AG57" s="3"/>
       <c r="AH57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3126,7 +3121,7 @@
       <c r="AG58" s="3"/>
       <c r="AH58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3162,7 +3157,7 @@
       <c r="AG59" s="3"/>
       <c r="AH59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3198,7 +3193,7 @@
       <c r="AG60" s="3"/>
       <c r="AH60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3234,7 +3229,7 @@
       <c r="AG61" s="3"/>
       <c r="AH61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3270,7 +3265,7 @@
       <c r="AG62" s="3"/>
       <c r="AH62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3306,7 +3301,7 @@
       <c r="AG63" s="3"/>
       <c r="AH63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3342,7 +3337,7 @@
       <c r="AG64" s="3"/>
       <c r="AH64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3378,7 +3373,7 @@
       <c r="AG65" s="3"/>
       <c r="AH65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3414,7 +3409,7 @@
       <c r="AG66" s="3"/>
       <c r="AH66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3450,7 +3445,7 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3486,7 +3481,7 @@
       <c r="AG68" s="3"/>
       <c r="AH68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3522,7 +3517,7 @@
       <c r="AG69" s="3"/>
       <c r="AH69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3558,7 +3553,7 @@
       <c r="AG70" s="3"/>
       <c r="AH70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3594,7 +3589,7 @@
       <c r="AG71" s="3"/>
       <c r="AH71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3630,7 +3625,7 @@
       <c r="AG72" s="3"/>
       <c r="AH72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3666,7 +3661,7 @@
       <c r="AG73" s="3"/>
       <c r="AH73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3702,7 +3697,7 @@
       <c r="AG74" s="3"/>
       <c r="AH74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3738,7 +3733,7 @@
       <c r="AG75" s="3"/>
       <c r="AH75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3774,7 +3769,7 @@
       <c r="AG76" s="3"/>
       <c r="AH76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3810,7 +3805,7 @@
       <c r="AG77" s="3"/>
       <c r="AH77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3846,7 +3841,7 @@
       <c r="AG78" s="3"/>
       <c r="AH78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3882,7 +3877,7 @@
       <c r="AG79" s="3"/>
       <c r="AH79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3918,7 +3913,7 @@
       <c r="AG80" s="3"/>
       <c r="AH80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3954,7 +3949,7 @@
       <c r="AG81" s="3"/>
       <c r="AH81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3990,7 +3985,7 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4026,7 +4021,7 @@
       <c r="AG83" s="3"/>
       <c r="AH83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4062,7 +4057,7 @@
       <c r="AG84" s="3"/>
       <c r="AH84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -4098,7 +4093,7 @@
       <c r="AG85" s="3"/>
       <c r="AH85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -4134,7 +4129,7 @@
       <c r="AG86" s="3"/>
       <c r="AH86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -4170,7 +4165,7 @@
       <c r="AG87" s="3"/>
       <c r="AH87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -4206,7 +4201,7 @@
       <c r="AG88" s="3"/>
       <c r="AH88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -4242,7 +4237,7 @@
       <c r="AG89" s="3"/>
       <c r="AH89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -4278,7 +4273,7 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -4314,7 +4309,7 @@
       <c r="AG91" s="3"/>
       <c r="AH91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -4350,7 +4345,7 @@
       <c r="AG92" s="3"/>
       <c r="AH92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -4386,7 +4381,7 @@
       <c r="AG93" s="3"/>
       <c r="AH93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -4422,7 +4417,7 @@
       <c r="AG94" s="3"/>
       <c r="AH94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -4458,7 +4453,7 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -4494,7 +4489,7 @@
       <c r="AG96" s="3"/>
       <c r="AH96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -4530,7 +4525,7 @@
       <c r="AG97" s="3"/>
       <c r="AH97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -4566,7 +4561,7 @@
       <c r="AG98" s="3"/>
       <c r="AH98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -4602,7 +4597,7 @@
       <c r="AG99" s="3"/>
       <c r="AH99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4638,7 +4633,7 @@
       <c r="AG100" s="3"/>
       <c r="AH100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4674,7 +4669,7 @@
       <c r="AG101" s="3"/>
       <c r="AH101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4710,7 +4705,7 @@
       <c r="AG102" s="3"/>
       <c r="AH102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4746,7 +4741,7 @@
       <c r="AG103" s="3"/>
       <c r="AH103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4782,7 +4777,7 @@
       <c r="AG104" s="3"/>
       <c r="AH104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4818,7 +4813,7 @@
       <c r="AG105" s="3"/>
       <c r="AH105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4854,7 +4849,7 @@
       <c r="AG106" s="3"/>
       <c r="AH106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4890,7 +4885,7 @@
       <c r="AG107" s="3"/>
       <c r="AH107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4926,7 +4921,7 @@
       <c r="AG108" s="3"/>
       <c r="AH108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4962,7 +4957,7 @@
       <c r="AG109" s="3"/>
       <c r="AH109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4998,7 +4993,7 @@
       <c r="AG110" s="3"/>
       <c r="AH110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -5034,7 +5029,7 @@
       <c r="AG111" s="3"/>
       <c r="AH111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -5070,7 +5065,7 @@
       <c r="AG112" s="3"/>
       <c r="AH112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -5106,7 +5101,7 @@
       <c r="AG113" s="3"/>
       <c r="AH113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -5142,7 +5137,7 @@
       <c r="AG114" s="3"/>
       <c r="AH114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -5178,7 +5173,7 @@
       <c r="AG115" s="3"/>
       <c r="AH115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -5214,7 +5209,7 @@
       <c r="AG116" s="3"/>
       <c r="AH116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -5250,7 +5245,7 @@
       <c r="AG117" s="3"/>
       <c r="AH117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -5286,7 +5281,7 @@
       <c r="AG118" s="3"/>
       <c r="AH118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -5322,7 +5317,7 @@
       <c r="AG119" s="3"/>
       <c r="AH119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -5358,7 +5353,7 @@
       <c r="AG120" s="3"/>
       <c r="AH120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -5394,7 +5389,7 @@
       <c r="AG121" s="3"/>
       <c r="AH121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -5430,7 +5425,7 @@
       <c r="AG122" s="3"/>
       <c r="AH122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -5466,7 +5461,7 @@
       <c r="AG123" s="3"/>
       <c r="AH123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -5502,7 +5497,7 @@
       <c r="AG124" s="3"/>
       <c r="AH124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -5538,7 +5533,7 @@
       <c r="AG125" s="3"/>
       <c r="AH125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -5574,7 +5569,7 @@
       <c r="AG126" s="3"/>
       <c r="AH126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -5610,7 +5605,7 @@
       <c r="AG127" s="3"/>
       <c r="AH127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -5646,7 +5641,7 @@
       <c r="AG128" s="3"/>
       <c r="AH128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5682,7 +5677,7 @@
       <c r="AG129" s="3"/>
       <c r="AH129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5718,7 +5713,7 @@
       <c r="AG130" s="3"/>
       <c r="AH130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5754,7 +5749,7 @@
       <c r="AG131" s="3"/>
       <c r="AH131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -5790,7 +5785,7 @@
       <c r="AG132" s="3"/>
       <c r="AH132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -5826,7 +5821,7 @@
       <c r="AG133" s="3"/>
       <c r="AH133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5862,7 +5857,7 @@
       <c r="AG134" s="3"/>
       <c r="AH134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5898,7 +5893,7 @@
       <c r="AG135" s="3"/>
       <c r="AH135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5934,7 +5929,7 @@
       <c r="AG136" s="3"/>
       <c r="AH136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5970,7 +5965,7 @@
       <c r="AG137" s="3"/>
       <c r="AH137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -6006,7 +6001,7 @@
       <c r="AG138" s="3"/>
       <c r="AH138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -6042,7 +6037,7 @@
       <c r="AG139" s="3"/>
       <c r="AH139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -6078,7 +6073,7 @@
       <c r="AG140" s="3"/>
       <c r="AH140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -6114,7 +6109,7 @@
       <c r="AG141" s="3"/>
       <c r="AH141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -6150,7 +6145,7 @@
       <c r="AG142" s="3"/>
       <c r="AH142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -6186,7 +6181,7 @@
       <c r="AG143" s="3"/>
       <c r="AH143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -6222,7 +6217,7 @@
       <c r="AG144" s="3"/>
       <c r="AH144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -6258,7 +6253,7 @@
       <c r="AG145" s="3"/>
       <c r="AH145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -6294,7 +6289,7 @@
       <c r="AG146" s="3"/>
       <c r="AH146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -6330,7 +6325,7 @@
       <c r="AG147" s="3"/>
       <c r="AH147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -6366,7 +6361,7 @@
       <c r="AG148" s="3"/>
       <c r="AH148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -6402,7 +6397,7 @@
       <c r="AG149" s="3"/>
       <c r="AH149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -6438,7 +6433,7 @@
       <c r="AG150" s="3"/>
       <c r="AH150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -6474,7 +6469,7 @@
       <c r="AG151" s="3"/>
       <c r="AH151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -6510,7 +6505,7 @@
       <c r="AG152" s="3"/>
       <c r="AH152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -6546,7 +6541,7 @@
       <c r="AG153" s="3"/>
       <c r="AH153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -6582,7 +6577,7 @@
       <c r="AG154" s="3"/>
       <c r="AH154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -6618,7 +6613,7 @@
       <c r="AG155" s="3"/>
       <c r="AH155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -6654,7 +6649,7 @@
       <c r="AG156" s="3"/>
       <c r="AH156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -6690,7 +6685,7 @@
       <c r="AG157" s="3"/>
       <c r="AH157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -6726,7 +6721,7 @@
       <c r="AG158" s="3"/>
       <c r="AH158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -6762,7 +6757,7 @@
       <c r="AG159" s="3"/>
       <c r="AH159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -6798,7 +6793,7 @@
       <c r="AG160" s="3"/>
       <c r="AH160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -6834,7 +6829,7 @@
       <c r="AG161" s="3"/>
       <c r="AH161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -6870,7 +6865,7 @@
       <c r="AG162" s="3"/>
       <c r="AH162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -6906,7 +6901,7 @@
       <c r="AG163" s="3"/>
       <c r="AH163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -6942,7 +6937,7 @@
       <c r="AG164" s="3"/>
       <c r="AH164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -6978,7 +6973,7 @@
       <c r="AG165" s="3"/>
       <c r="AH165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -7014,7 +7009,7 @@
       <c r="AG166" s="3"/>
       <c r="AH166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -7050,7 +7045,7 @@
       <c r="AG167" s="3"/>
       <c r="AH167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -7086,7 +7081,7 @@
       <c r="AG168" s="3"/>
       <c r="AH168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -7122,7 +7117,7 @@
       <c r="AG169" s="3"/>
       <c r="AH169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -7158,7 +7153,7 @@
       <c r="AG170" s="3"/>
       <c r="AH170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -7194,7 +7189,7 @@
       <c r="AG171" s="3"/>
       <c r="AH171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -7230,7 +7225,7 @@
       <c r="AG172" s="3"/>
       <c r="AH172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -7266,7 +7261,7 @@
       <c r="AG173" s="3"/>
       <c r="AH173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -7302,7 +7297,7 @@
       <c r="AG174" s="3"/>
       <c r="AH174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -7338,7 +7333,7 @@
       <c r="AG175" s="3"/>
       <c r="AH175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -7374,7 +7369,7 @@
       <c r="AG176" s="3"/>
       <c r="AH176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -7410,7 +7405,7 @@
       <c r="AG177" s="3"/>
       <c r="AH177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -7446,7 +7441,7 @@
       <c r="AG178" s="3"/>
       <c r="AH178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -7482,7 +7477,7 @@
       <c r="AG179" s="3"/>
       <c r="AH179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -7518,7 +7513,7 @@
       <c r="AG180" s="3"/>
       <c r="AH180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -7554,7 +7549,7 @@
       <c r="AG181" s="3"/>
       <c r="AH181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -7590,7 +7585,7 @@
       <c r="AG182" s="3"/>
       <c r="AH182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -7626,7 +7621,7 @@
       <c r="AG183" s="3"/>
       <c r="AH183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -7662,7 +7657,7 @@
       <c r="AG184" s="3"/>
       <c r="AH184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -7698,7 +7693,7 @@
       <c r="AG185" s="3"/>
       <c r="AH185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -7734,7 +7729,7 @@
       <c r="AG186" s="3"/>
       <c r="AH186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -7770,7 +7765,7 @@
       <c r="AG187" s="3"/>
       <c r="AH187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -7806,7 +7801,7 @@
       <c r="AG188" s="3"/>
       <c r="AH188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -7842,7 +7837,7 @@
       <c r="AG189" s="3"/>
       <c r="AH189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -7878,7 +7873,7 @@
       <c r="AG190" s="3"/>
       <c r="AH190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -7914,7 +7909,7 @@
       <c r="AG191" s="3"/>
       <c r="AH191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -7950,7 +7945,7 @@
       <c r="AG192" s="3"/>
       <c r="AH192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -7986,7 +7981,7 @@
       <c r="AG193" s="3"/>
       <c r="AH193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -8022,7 +8017,7 @@
       <c r="AG194" s="3"/>
       <c r="AH194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -8058,7 +8053,7 @@
       <c r="AG195" s="3"/>
       <c r="AH195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -8094,7 +8089,7 @@
       <c r="AG196" s="3"/>
       <c r="AH196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -8130,7 +8125,7 @@
       <c r="AG197" s="3"/>
       <c r="AH197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -8166,7 +8161,7 @@
       <c r="AG198" s="3"/>
       <c r="AH198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -8202,7 +8197,7 @@
       <c r="AG199" s="3"/>
       <c r="AH199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -8238,7 +8233,7 @@
       <c r="AG200" s="3"/>
       <c r="AH200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -8274,7 +8269,7 @@
       <c r="AG201" s="3"/>
       <c r="AH201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -8310,7 +8305,7 @@
       <c r="AG202" s="3"/>
       <c r="AH202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -8346,7 +8341,7 @@
       <c r="AG203" s="3"/>
       <c r="AH203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -8382,7 +8377,7 @@
       <c r="AG204" s="3"/>
       <c r="AH204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -8418,7 +8413,7 @@
       <c r="AG205" s="3"/>
       <c r="AH205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -8454,7 +8449,7 @@
       <c r="AG206" s="3"/>
       <c r="AH206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -8490,7 +8485,7 @@
       <c r="AG207" s="3"/>
       <c r="AH207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -8526,7 +8521,7 @@
       <c r="AG208" s="3"/>
       <c r="AH208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -8562,7 +8557,7 @@
       <c r="AG209" s="3"/>
       <c r="AH209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -8598,7 +8593,7 @@
       <c r="AG210" s="3"/>
       <c r="AH210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -8634,7 +8629,7 @@
       <c r="AG211" s="3"/>
       <c r="AH211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -8670,7 +8665,7 @@
       <c r="AG212" s="3"/>
       <c r="AH212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -8706,7 +8701,7 @@
       <c r="AG213" s="3"/>
       <c r="AH213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -8742,7 +8737,7 @@
       <c r="AG214" s="3"/>
       <c r="AH214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -8778,7 +8773,7 @@
       <c r="AG215" s="3"/>
       <c r="AH215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -8814,7 +8809,7 @@
       <c r="AG216" s="3"/>
       <c r="AH216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -8850,7 +8845,7 @@
       <c r="AG217" s="3"/>
       <c r="AH217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -8886,7 +8881,7 @@
       <c r="AG218" s="3"/>
       <c r="AH218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -8922,7 +8917,7 @@
       <c r="AG219" s="3"/>
       <c r="AH219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -8958,7 +8953,7 @@
       <c r="AG220" s="3"/>
       <c r="AH220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -8994,7 +8989,7 @@
       <c r="AG221" s="3"/>
       <c r="AH221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -9030,7 +9025,7 @@
       <c r="AG222" s="3"/>
       <c r="AH222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -9066,7 +9061,7 @@
       <c r="AG223" s="3"/>
       <c r="AH223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -9102,7 +9097,7 @@
       <c r="AG224" s="3"/>
       <c r="AH224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -9138,7 +9133,7 @@
       <c r="AG225" s="3"/>
       <c r="AH225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -9174,7 +9169,7 @@
       <c r="AG226" s="3"/>
       <c r="AH226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -9210,7 +9205,7 @@
       <c r="AG227" s="3"/>
       <c r="AH227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -9246,7 +9241,7 @@
       <c r="AG228" s="3"/>
       <c r="AH228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -9282,7 +9277,7 @@
       <c r="AG229" s="3"/>
       <c r="AH229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -9318,7 +9313,7 @@
       <c r="AG230" s="3"/>
       <c r="AH230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -9354,7 +9349,7 @@
       <c r="AG231" s="3"/>
       <c r="AH231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -9390,7 +9385,7 @@
       <c r="AG232" s="3"/>
       <c r="AH232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -9426,7 +9421,7 @@
       <c r="AG233" s="3"/>
       <c r="AH233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -9462,7 +9457,7 @@
       <c r="AG234" s="3"/>
       <c r="AH234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -9498,7 +9493,7 @@
       <c r="AG235" s="3"/>
       <c r="AH235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -9534,7 +9529,7 @@
       <c r="AG236" s="3"/>
       <c r="AH236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -9570,7 +9565,7 @@
       <c r="AG237" s="3"/>
       <c r="AH237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -9606,7 +9601,7 @@
       <c r="AG238" s="3"/>
       <c r="AH238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -9642,7 +9637,7 @@
       <c r="AG239" s="3"/>
       <c r="AH239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -9678,7 +9673,7 @@
       <c r="AG240" s="3"/>
       <c r="AH240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -9714,7 +9709,7 @@
       <c r="AG241" s="3"/>
       <c r="AH241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -9750,7 +9745,7 @@
       <c r="AG242" s="3"/>
       <c r="AH242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -9786,7 +9781,7 @@
       <c r="AG243" s="3"/>
       <c r="AH243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -9822,7 +9817,7 @@
       <c r="AG244" s="3"/>
       <c r="AH244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -9858,7 +9853,7 @@
       <c r="AG245" s="3"/>
       <c r="AH245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -9894,7 +9889,7 @@
       <c r="AG246" s="3"/>
       <c r="AH246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -9930,7 +9925,7 @@
       <c r="AG247" s="3"/>
       <c r="AH247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -9966,7 +9961,7 @@
       <c r="AG248" s="3"/>
       <c r="AH248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -10002,7 +9997,7 @@
       <c r="AG249" s="3"/>
       <c r="AH249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -10038,7 +10033,7 @@
       <c r="AG250" s="3"/>
       <c r="AH250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -10074,7 +10069,7 @@
       <c r="AG251" s="3"/>
       <c r="AH251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -10110,7 +10105,7 @@
       <c r="AG252" s="3"/>
       <c r="AH252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -10146,7 +10141,7 @@
       <c r="AG253" s="3"/>
       <c r="AH253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -10182,7 +10177,7 @@
       <c r="AG254" s="3"/>
       <c r="AH254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -10218,7 +10213,7 @@
       <c r="AG255" s="3"/>
       <c r="AH255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -10254,7 +10249,7 @@
       <c r="AG256" s="3"/>
       <c r="AH256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -10290,7 +10285,7 @@
       <c r="AG257" s="3"/>
       <c r="AH257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -10326,7 +10321,7 @@
       <c r="AG258" s="3"/>
       <c r="AH258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -10362,7 +10357,7 @@
       <c r="AG259" s="3"/>
       <c r="AH259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -10398,7 +10393,7 @@
       <c r="AG260" s="3"/>
       <c r="AH260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -10434,7 +10429,7 @@
       <c r="AG261" s="3"/>
       <c r="AH261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -10470,7 +10465,7 @@
       <c r="AG262" s="3"/>
       <c r="AH262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -10506,7 +10501,7 @@
       <c r="AG263" s="3"/>
       <c r="AH263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -10542,7 +10537,7 @@
       <c r="AG264" s="3"/>
       <c r="AH264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -10578,7 +10573,7 @@
       <c r="AG265" s="3"/>
       <c r="AH265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -10614,7 +10609,7 @@
       <c r="AG266" s="3"/>
       <c r="AH266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -10650,7 +10645,7 @@
       <c r="AG267" s="3"/>
       <c r="AH267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -10686,7 +10681,7 @@
       <c r="AG268" s="3"/>
       <c r="AH268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -10722,7 +10717,7 @@
       <c r="AG269" s="3"/>
       <c r="AH269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -10758,7 +10753,7 @@
       <c r="AG270" s="3"/>
       <c r="AH270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -10794,7 +10789,7 @@
       <c r="AG271" s="3"/>
       <c r="AH271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -10830,7 +10825,7 @@
       <c r="AG272" s="3"/>
       <c r="AH272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -10866,7 +10861,7 @@
       <c r="AG273" s="3"/>
       <c r="AH273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -10902,7 +10897,7 @@
       <c r="AG274" s="3"/>
       <c r="AH274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -10938,7 +10933,7 @@
       <c r="AG275" s="3"/>
       <c r="AH275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -10974,7 +10969,7 @@
       <c r="AG276" s="3"/>
       <c r="AH276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -11010,7 +11005,7 @@
       <c r="AG277" s="3"/>
       <c r="AH277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -11046,7 +11041,7 @@
       <c r="AG278" s="3"/>
       <c r="AH278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -11082,7 +11077,7 @@
       <c r="AG279" s="3"/>
       <c r="AH279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -11118,7 +11113,7 @@
       <c r="AG280" s="3"/>
       <c r="AH280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -11154,7 +11149,7 @@
       <c r="AG281" s="3"/>
       <c r="AH281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -11190,7 +11185,7 @@
       <c r="AG282" s="3"/>
       <c r="AH282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -11226,7 +11221,7 @@
       <c r="AG283" s="3"/>
       <c r="AH283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -11262,7 +11257,7 @@
       <c r="AG284" s="3"/>
       <c r="AH284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -11298,7 +11293,7 @@
       <c r="AG285" s="3"/>
       <c r="AH285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -11334,7 +11329,7 @@
       <c r="AG286" s="3"/>
       <c r="AH286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -11370,7 +11365,7 @@
       <c r="AG287" s="3"/>
       <c r="AH287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -11406,7 +11401,7 @@
       <c r="AG288" s="3"/>
       <c r="AH288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -11442,7 +11437,7 @@
       <c r="AG289" s="3"/>
       <c r="AH289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -11478,7 +11473,7 @@
       <c r="AG290" s="3"/>
       <c r="AH290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -11514,7 +11509,7 @@
       <c r="AG291" s="3"/>
       <c r="AH291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -11550,7 +11545,7 @@
       <c r="AG292" s="3"/>
       <c r="AH292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -11586,7 +11581,7 @@
       <c r="AG293" s="3"/>
       <c r="AH293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -11622,7 +11617,7 @@
       <c r="AG294" s="3"/>
       <c r="AH294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -11658,7 +11653,7 @@
       <c r="AG295" s="3"/>
       <c r="AH295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -11694,7 +11689,7 @@
       <c r="AG296" s="3"/>
       <c r="AH296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -11730,7 +11725,7 @@
       <c r="AG297" s="3"/>
       <c r="AH297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -11766,7 +11761,7 @@
       <c r="AG298" s="3"/>
       <c r="AH298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -11802,7 +11797,7 @@
       <c r="AG299" s="3"/>
       <c r="AH299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -11838,7 +11833,7 @@
       <c r="AG300" s="3"/>
       <c r="AH300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -11874,7 +11869,7 @@
       <c r="AG301" s="3"/>
       <c r="AH301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -11910,7 +11905,7 @@
       <c r="AG302" s="3"/>
       <c r="AH302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -11946,7 +11941,7 @@
       <c r="AG303" s="3"/>
       <c r="AH303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -11982,7 +11977,7 @@
       <c r="AG304" s="3"/>
       <c r="AH304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -12018,7 +12013,7 @@
       <c r="AG305" s="3"/>
       <c r="AH305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -12054,7 +12049,7 @@
       <c r="AG306" s="3"/>
       <c r="AH306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -12090,7 +12085,7 @@
       <c r="AG307" s="3"/>
       <c r="AH307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -12126,7 +12121,7 @@
       <c r="AG308" s="3"/>
       <c r="AH308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -12162,7 +12157,7 @@
       <c r="AG309" s="3"/>
       <c r="AH309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -12198,7 +12193,7 @@
       <c r="AG310" s="3"/>
       <c r="AH310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -12234,7 +12229,7 @@
       <c r="AG311" s="3"/>
       <c r="AH311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -12270,7 +12265,7 @@
       <c r="AG312" s="3"/>
       <c r="AH312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -12306,7 +12301,7 @@
       <c r="AG313" s="3"/>
       <c r="AH313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -12342,7 +12337,7 @@
       <c r="AG314" s="3"/>
       <c r="AH314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -12378,7 +12373,7 @@
       <c r="AG315" s="3"/>
       <c r="AH315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -12414,7 +12409,7 @@
       <c r="AG316" s="3"/>
       <c r="AH316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -12450,7 +12445,7 @@
       <c r="AG317" s="3"/>
       <c r="AH317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -12486,7 +12481,7 @@
       <c r="AG318" s="3"/>
       <c r="AH318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -12522,7 +12517,7 @@
       <c r="AG319" s="3"/>
       <c r="AH319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -12558,7 +12553,7 @@
       <c r="AG320" s="3"/>
       <c r="AH320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -12594,7 +12589,7 @@
       <c r="AG321" s="3"/>
       <c r="AH321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -12630,7 +12625,7 @@
       <c r="AG322" s="3"/>
       <c r="AH322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -12666,7 +12661,7 @@
       <c r="AG323" s="3"/>
       <c r="AH323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -12702,7 +12697,7 @@
       <c r="AG324" s="3"/>
       <c r="AH324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -12738,7 +12733,7 @@
       <c r="AG325" s="3"/>
       <c r="AH325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -12774,7 +12769,7 @@
       <c r="AG326" s="3"/>
       <c r="AH326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -12810,7 +12805,7 @@
       <c r="AG327" s="3"/>
       <c r="AH327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -12846,7 +12841,7 @@
       <c r="AG328" s="3"/>
       <c r="AH328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -12882,7 +12877,7 @@
       <c r="AG329" s="3"/>
       <c r="AH329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -12918,7 +12913,7 @@
       <c r="AG330" s="3"/>
       <c r="AH330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -12954,7 +12949,7 @@
       <c r="AG331" s="3"/>
       <c r="AH331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -12990,7 +12985,7 @@
       <c r="AG332" s="3"/>
       <c r="AH332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -13026,7 +13021,7 @@
       <c r="AG333" s="3"/>
       <c r="AH333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -13062,7 +13057,7 @@
       <c r="AG334" s="3"/>
       <c r="AH334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -13098,7 +13093,7 @@
       <c r="AG335" s="3"/>
       <c r="AH335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -13134,7 +13129,7 @@
       <c r="AG336" s="3"/>
       <c r="AH336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -13170,7 +13165,7 @@
       <c r="AG337" s="3"/>
       <c r="AH337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -13206,7 +13201,7 @@
       <c r="AG338" s="3"/>
       <c r="AH338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -13242,7 +13237,7 @@
       <c r="AG339" s="3"/>
       <c r="AH339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -13278,7 +13273,7 @@
       <c r="AG340" s="3"/>
       <c r="AH340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -13314,7 +13309,7 @@
       <c r="AG341" s="3"/>
       <c r="AH341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -13350,7 +13345,7 @@
       <c r="AG342" s="3"/>
       <c r="AH342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -13386,7 +13381,7 @@
       <c r="AG343" s="3"/>
       <c r="AH343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -13422,7 +13417,7 @@
       <c r="AG344" s="3"/>
       <c r="AH344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -13458,7 +13453,7 @@
       <c r="AG345" s="3"/>
       <c r="AH345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -13494,7 +13489,7 @@
       <c r="AG346" s="3"/>
       <c r="AH346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -13530,7 +13525,7 @@
       <c r="AG347" s="3"/>
       <c r="AH347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -13566,7 +13561,7 @@
       <c r="AG348" s="3"/>
       <c r="AH348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -13602,7 +13597,7 @@
       <c r="AG349" s="3"/>
       <c r="AH349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -13638,7 +13633,7 @@
       <c r="AG350" s="3"/>
       <c r="AH350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -13674,7 +13669,7 @@
       <c r="AG351" s="3"/>
       <c r="AH351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -13710,7 +13705,7 @@
       <c r="AG352" s="3"/>
       <c r="AH352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -13746,7 +13741,7 @@
       <c r="AG353" s="3"/>
       <c r="AH353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -13782,7 +13777,7 @@
       <c r="AG354" s="3"/>
       <c r="AH354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -13818,7 +13813,7 @@
       <c r="AG355" s="3"/>
       <c r="AH355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -13854,7 +13849,7 @@
       <c r="AG356" s="3"/>
       <c r="AH356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -13890,7 +13885,7 @@
       <c r="AG357" s="3"/>
       <c r="AH357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -13926,7 +13921,7 @@
       <c r="AG358" s="3"/>
       <c r="AH358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -13962,7 +13957,7 @@
       <c r="AG359" s="3"/>
       <c r="AH359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -13998,7 +13993,7 @@
       <c r="AG360" s="3"/>
       <c r="AH360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -14034,7 +14029,7 @@
       <c r="AG361" s="3"/>
       <c r="AH361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -14070,7 +14065,7 @@
       <c r="AG362" s="3"/>
       <c r="AH362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -14106,7 +14101,7 @@
       <c r="AG363" s="3"/>
       <c r="AH363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -14142,7 +14137,7 @@
       <c r="AG364" s="3"/>
       <c r="AH364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -14178,7 +14173,7 @@
       <c r="AG365" s="3"/>
       <c r="AH365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -14214,7 +14209,7 @@
       <c r="AG366" s="3"/>
       <c r="AH366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -14250,7 +14245,7 @@
       <c r="AG367" s="3"/>
       <c r="AH367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -14286,7 +14281,7 @@
       <c r="AG368" s="3"/>
       <c r="AH368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -14322,7 +14317,7 @@
       <c r="AG369" s="3"/>
       <c r="AH369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -14358,7 +14353,7 @@
       <c r="AG370" s="3"/>
       <c r="AH370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -14394,7 +14389,7 @@
       <c r="AG371" s="3"/>
       <c r="AH371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -14430,7 +14425,7 @@
       <c r="AG372" s="3"/>
       <c r="AH372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -14466,7 +14461,7 @@
       <c r="AG373" s="3"/>
       <c r="AH373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -14502,7 +14497,7 @@
       <c r="AG374" s="3"/>
       <c r="AH374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -14538,7 +14533,7 @@
       <c r="AG375" s="3"/>
       <c r="AH375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -14574,7 +14569,7 @@
       <c r="AG376" s="3"/>
       <c r="AH376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -14610,7 +14605,7 @@
       <c r="AG377" s="3"/>
       <c r="AH377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -14646,7 +14641,7 @@
       <c r="AG378" s="3"/>
       <c r="AH378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -14682,7 +14677,7 @@
       <c r="AG379" s="3"/>
       <c r="AH379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -14718,7 +14713,7 @@
       <c r="AG380" s="3"/>
       <c r="AH380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -14754,7 +14749,7 @@
       <c r="AG381" s="3"/>
       <c r="AH381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -14790,7 +14785,7 @@
       <c r="AG382" s="3"/>
       <c r="AH382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -14826,7 +14821,7 @@
       <c r="AG383" s="3"/>
       <c r="AH383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -14862,7 +14857,7 @@
       <c r="AG384" s="3"/>
       <c r="AH384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -14898,7 +14893,7 @@
       <c r="AG385" s="3"/>
       <c r="AH385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -14934,7 +14929,7 @@
       <c r="AG386" s="3"/>
       <c r="AH386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -14970,7 +14965,7 @@
       <c r="AG387" s="3"/>
       <c r="AH387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -15006,7 +15001,7 @@
       <c r="AG388" s="3"/>
       <c r="AH388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -15042,7 +15037,7 @@
       <c r="AG389" s="3"/>
       <c r="AH389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -15078,7 +15073,7 @@
       <c r="AG390" s="3"/>
       <c r="AH390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -15114,7 +15109,7 @@
       <c r="AG391" s="3"/>
       <c r="AH391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -15150,7 +15145,7 @@
       <c r="AG392" s="3"/>
       <c r="AH392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -15186,7 +15181,7 @@
       <c r="AG393" s="3"/>
       <c r="AH393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -15222,7 +15217,7 @@
       <c r="AG394" s="3"/>
       <c r="AH394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -15258,7 +15253,7 @@
       <c r="AG395" s="3"/>
       <c r="AH395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -15294,7 +15289,7 @@
       <c r="AG396" s="3"/>
       <c r="AH396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -15330,7 +15325,7 @@
       <c r="AG397" s="3"/>
       <c r="AH397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -15366,7 +15361,7 @@
       <c r="AG398" s="3"/>
       <c r="AH398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -15402,7 +15397,7 @@
       <c r="AG399" s="3"/>
       <c r="AH399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -15438,7 +15433,7 @@
       <c r="AG400" s="3"/>
       <c r="AH400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -15474,7 +15469,7 @@
       <c r="AG401" s="3"/>
       <c r="AH401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -15510,7 +15505,7 @@
       <c r="AG402" s="3"/>
       <c r="AH402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -15546,7 +15541,7 @@
       <c r="AG403" s="3"/>
       <c r="AH403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -15582,7 +15577,7 @@
       <c r="AG404" s="3"/>
       <c r="AH404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -15618,7 +15613,7 @@
       <c r="AG405" s="3"/>
       <c r="AH405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -15654,7 +15649,7 @@
       <c r="AG406" s="3"/>
       <c r="AH406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -15690,7 +15685,7 @@
       <c r="AG407" s="3"/>
       <c r="AH407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -15726,7 +15721,7 @@
       <c r="AG408" s="3"/>
       <c r="AH408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -15762,7 +15757,7 @@
       <c r="AG409" s="3"/>
       <c r="AH409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -15798,7 +15793,7 @@
       <c r="AG410" s="3"/>
       <c r="AH410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -15834,7 +15829,7 @@
       <c r="AG411" s="3"/>
       <c r="AH411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -15870,7 +15865,7 @@
       <c r="AG412" s="3"/>
       <c r="AH412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -15906,7 +15901,7 @@
       <c r="AG413" s="3"/>
       <c r="AH413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -15942,7 +15937,7 @@
       <c r="AG414" s="3"/>
       <c r="AH414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -15978,7 +15973,7 @@
       <c r="AG415" s="3"/>
       <c r="AH415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -16014,7 +16009,7 @@
       <c r="AG416" s="3"/>
       <c r="AH416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -16050,7 +16045,7 @@
       <c r="AG417" s="3"/>
       <c r="AH417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -16086,7 +16081,7 @@
       <c r="AG418" s="3"/>
       <c r="AH418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -16122,7 +16117,7 @@
       <c r="AG419" s="3"/>
       <c r="AH419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -16158,7 +16153,7 @@
       <c r="AG420" s="3"/>
       <c r="AH420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -16194,7 +16189,7 @@
       <c r="AG421" s="3"/>
       <c r="AH421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -16230,7 +16225,7 @@
       <c r="AG422" s="3"/>
       <c r="AH422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -16266,7 +16261,7 @@
       <c r="AG423" s="3"/>
       <c r="AH423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -16302,7 +16297,7 @@
       <c r="AG424" s="3"/>
       <c r="AH424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -16338,7 +16333,7 @@
       <c r="AG425" s="3"/>
       <c r="AH425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -16374,7 +16369,7 @@
       <c r="AG426" s="3"/>
       <c r="AH426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -16410,7 +16405,7 @@
       <c r="AG427" s="3"/>
       <c r="AH427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -16446,7 +16441,7 @@
       <c r="AG428" s="3"/>
       <c r="AH428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -16482,7 +16477,7 @@
       <c r="AG429" s="3"/>
       <c r="AH429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -16518,7 +16513,7 @@
       <c r="AG430" s="3"/>
       <c r="AH430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -16554,7 +16549,7 @@
       <c r="AG431" s="3"/>
       <c r="AH431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -16590,7 +16585,7 @@
       <c r="AG432" s="3"/>
       <c r="AH432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -16626,7 +16621,7 @@
       <c r="AG433" s="3"/>
       <c r="AH433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -16662,7 +16657,7 @@
       <c r="AG434" s="3"/>
       <c r="AH434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -16698,7 +16693,7 @@
       <c r="AG435" s="3"/>
       <c r="AH435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -16734,7 +16729,7 @@
       <c r="AG436" s="3"/>
       <c r="AH436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -16770,7 +16765,7 @@
       <c r="AG437" s="3"/>
       <c r="AH437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -16806,7 +16801,7 @@
       <c r="AG438" s="3"/>
       <c r="AH438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -16842,7 +16837,7 @@
       <c r="AG439" s="3"/>
       <c r="AH439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -16878,7 +16873,7 @@
       <c r="AG440" s="3"/>
       <c r="AH440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -16914,7 +16909,7 @@
       <c r="AG441" s="3"/>
       <c r="AH441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -16950,7 +16945,7 @@
       <c r="AG442" s="3"/>
       <c r="AH442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -16986,7 +16981,7 @@
       <c r="AG443" s="3"/>
       <c r="AH443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -17022,7 +17017,7 @@
       <c r="AG444" s="3"/>
       <c r="AH444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -17058,7 +17053,7 @@
       <c r="AG445" s="3"/>
       <c r="AH445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -17094,7 +17089,7 @@
       <c r="AG446" s="3"/>
       <c r="AH446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -17130,7 +17125,7 @@
       <c r="AG447" s="3"/>
       <c r="AH447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -17166,7 +17161,7 @@
       <c r="AG448" s="3"/>
       <c r="AH448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -17202,7 +17197,7 @@
       <c r="AG449" s="3"/>
       <c r="AH449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -17238,7 +17233,7 @@
       <c r="AG450" s="3"/>
       <c r="AH450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -17274,7 +17269,7 @@
       <c r="AG451" s="3"/>
       <c r="AH451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -17310,7 +17305,7 @@
       <c r="AG452" s="3"/>
       <c r="AH452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -17346,7 +17341,7 @@
       <c r="AG453" s="3"/>
       <c r="AH453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -17382,7 +17377,7 @@
       <c r="AG454" s="3"/>
       <c r="AH454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -17418,7 +17413,7 @@
       <c r="AG455" s="3"/>
       <c r="AH455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -17454,7 +17449,7 @@
       <c r="AG456" s="3"/>
       <c r="AH456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -17490,7 +17485,7 @@
       <c r="AG457" s="3"/>
       <c r="AH457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -17526,7 +17521,7 @@
       <c r="AG458" s="3"/>
       <c r="AH458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -17562,7 +17557,7 @@
       <c r="AG459" s="3"/>
       <c r="AH459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -17598,7 +17593,7 @@
       <c r="AG460" s="3"/>
       <c r="AH460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -17634,7 +17629,7 @@
       <c r="AG461" s="3"/>
       <c r="AH461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -17670,7 +17665,7 @@
       <c r="AG462" s="3"/>
       <c r="AH462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -17706,7 +17701,7 @@
       <c r="AG463" s="3"/>
       <c r="AH463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -17742,7 +17737,7 @@
       <c r="AG464" s="3"/>
       <c r="AH464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -17778,7 +17773,7 @@
       <c r="AG465" s="3"/>
       <c r="AH465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -17814,7 +17809,7 @@
       <c r="AG466" s="3"/>
       <c r="AH466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -17850,7 +17845,7 @@
       <c r="AG467" s="3"/>
       <c r="AH467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -17886,7 +17881,7 @@
       <c r="AG468" s="3"/>
       <c r="AH468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -17922,7 +17917,7 @@
       <c r="AG469" s="3"/>
       <c r="AH469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -17958,7 +17953,7 @@
       <c r="AG470" s="3"/>
       <c r="AH470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -17994,7 +17989,7 @@
       <c r="AG471" s="3"/>
       <c r="AH471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -18030,7 +18025,7 @@
       <c r="AG472" s="3"/>
       <c r="AH472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -18066,7 +18061,7 @@
       <c r="AG473" s="3"/>
       <c r="AH473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -18102,7 +18097,7 @@
       <c r="AG474" s="3"/>
       <c r="AH474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -18138,7 +18133,7 @@
       <c r="AG475" s="3"/>
       <c r="AH475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -18174,7 +18169,7 @@
       <c r="AG476" s="3"/>
       <c r="AH476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -18210,7 +18205,7 @@
       <c r="AG477" s="3"/>
       <c r="AH477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -18246,7 +18241,7 @@
       <c r="AG478" s="3"/>
       <c r="AH478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -18282,7 +18277,7 @@
       <c r="AG479" s="3"/>
       <c r="AH479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -18318,7 +18313,7 @@
       <c r="AG480" s="3"/>
       <c r="AH480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -18354,7 +18349,7 @@
       <c r="AG481" s="3"/>
       <c r="AH481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -18390,7 +18385,7 @@
       <c r="AG482" s="3"/>
       <c r="AH482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -18426,7 +18421,7 @@
       <c r="AG483" s="3"/>
       <c r="AH483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -18462,7 +18457,7 @@
       <c r="AG484" s="3"/>
       <c r="AH484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -18498,7 +18493,7 @@
       <c r="AG485" s="3"/>
       <c r="AH485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -18534,7 +18529,7 @@
       <c r="AG486" s="3"/>
       <c r="AH486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -18570,7 +18565,7 @@
       <c r="AG487" s="3"/>
       <c r="AH487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -18606,7 +18601,7 @@
       <c r="AG488" s="3"/>
       <c r="AH488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -18642,7 +18637,7 @@
       <c r="AG489" s="3"/>
       <c r="AH489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -18678,7 +18673,7 @@
       <c r="AG490" s="3"/>
       <c r="AH490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -18714,7 +18709,7 @@
       <c r="AG491" s="3"/>
       <c r="AH491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -18750,7 +18745,7 @@
       <c r="AG492" s="3"/>
       <c r="AH492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -18786,7 +18781,7 @@
       <c r="AG493" s="3"/>
       <c r="AH493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -18822,7 +18817,7 @@
       <c r="AG494" s="3"/>
       <c r="AH494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -18858,7 +18853,7 @@
       <c r="AG495" s="3"/>
       <c r="AH495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -18894,7 +18889,7 @@
       <c r="AG496" s="3"/>
       <c r="AH496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -18930,7 +18925,7 @@
       <c r="AG497" s="3"/>
       <c r="AH497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -18966,7 +18961,7 @@
       <c r="AG498" s="3"/>
       <c r="AH498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -19002,7 +18997,7 @@
       <c r="AG499" s="3"/>
       <c r="AH499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -19038,7 +19033,7 @@
       <c r="AG500" s="3"/>
       <c r="AH500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -19074,7 +19069,7 @@
       <c r="AG501" s="3"/>
       <c r="AH501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -19110,7 +19105,7 @@
       <c r="AG502" s="3"/>
       <c r="AH502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -19146,7 +19141,7 @@
       <c r="AG503" s="3"/>
       <c r="AH503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -19182,7 +19177,7 @@
       <c r="AG504" s="3"/>
       <c r="AH504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -19218,7 +19213,7 @@
       <c r="AG505" s="3"/>
       <c r="AH505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -19254,7 +19249,7 @@
       <c r="AG506" s="3"/>
       <c r="AH506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -19290,7 +19285,7 @@
       <c r="AG507" s="3"/>
       <c r="AH507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -19326,7 +19321,7 @@
       <c r="AG508" s="3"/>
       <c r="AH508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -19362,7 +19357,7 @@
       <c r="AG509" s="3"/>
       <c r="AH509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -19398,7 +19393,7 @@
       <c r="AG510" s="3"/>
       <c r="AH510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -19434,7 +19429,7 @@
       <c r="AG511" s="3"/>
       <c r="AH511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -19470,7 +19465,7 @@
       <c r="AG512" s="3"/>
       <c r="AH512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -19506,7 +19501,7 @@
       <c r="AG513" s="3"/>
       <c r="AH513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -19542,7 +19537,7 @@
       <c r="AG514" s="3"/>
       <c r="AH514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -19578,7 +19573,7 @@
       <c r="AG515" s="3"/>
       <c r="AH515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -19614,7 +19609,7 @@
       <c r="AG516" s="3"/>
       <c r="AH516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -19650,7 +19645,7 @@
       <c r="AG517" s="3"/>
       <c r="AH517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -19686,7 +19681,7 @@
       <c r="AG518" s="3"/>
       <c r="AH518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -19722,7 +19717,7 @@
       <c r="AG519" s="3"/>
       <c r="AH519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -19758,7 +19753,7 @@
       <c r="AG520" s="3"/>
       <c r="AH520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -19794,7 +19789,7 @@
       <c r="AG521" s="3"/>
       <c r="AH521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -19830,7 +19825,7 @@
       <c r="AG522" s="3"/>
       <c r="AH522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -19866,7 +19861,7 @@
       <c r="AG523" s="3"/>
       <c r="AH523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -19902,7 +19897,7 @@
       <c r="AG524" s="3"/>
       <c r="AH524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -19938,7 +19933,7 @@
       <c r="AG525" s="3"/>
       <c r="AH525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -19974,7 +19969,7 @@
       <c r="AG526" s="3"/>
       <c r="AH526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -20010,7 +20005,7 @@
       <c r="AG527" s="3"/>
       <c r="AH527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -20046,7 +20041,7 @@
       <c r="AG528" s="3"/>
       <c r="AH528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -20082,7 +20077,7 @@
       <c r="AG529" s="3"/>
       <c r="AH529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -20118,7 +20113,7 @@
       <c r="AG530" s="3"/>
       <c r="AH530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -20154,7 +20149,7 @@
       <c r="AG531" s="3"/>
       <c r="AH531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -20190,7 +20185,7 @@
       <c r="AG532" s="3"/>
       <c r="AH532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -20226,7 +20221,7 @@
       <c r="AG533" s="3"/>
       <c r="AH533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -20262,7 +20257,7 @@
       <c r="AG534" s="3"/>
       <c r="AH534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -20298,7 +20293,7 @@
       <c r="AG535" s="3"/>
       <c r="AH535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -20334,7 +20329,7 @@
       <c r="AG536" s="3"/>
       <c r="AH536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -20370,7 +20365,7 @@
       <c r="AG537" s="3"/>
       <c r="AH537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -20406,7 +20401,7 @@
       <c r="AG538" s="3"/>
       <c r="AH538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -20442,7 +20437,7 @@
       <c r="AG539" s="3"/>
       <c r="AH539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -20478,7 +20473,7 @@
       <c r="AG540" s="3"/>
       <c r="AH540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -20514,7 +20509,7 @@
       <c r="AG541" s="3"/>
       <c r="AH541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -20550,7 +20545,7 @@
       <c r="AG542" s="3"/>
       <c r="AH542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -20586,7 +20581,7 @@
       <c r="AG543" s="3"/>
       <c r="AH543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -20622,7 +20617,7 @@
       <c r="AG544" s="3"/>
       <c r="AH544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -20658,7 +20653,7 @@
       <c r="AG545" s="3"/>
       <c r="AH545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -20694,7 +20689,7 @@
       <c r="AG546" s="3"/>
       <c r="AH546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -20730,7 +20725,7 @@
       <c r="AG547" s="3"/>
       <c r="AH547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -20766,7 +20761,7 @@
       <c r="AG548" s="3"/>
       <c r="AH548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -20802,7 +20797,7 @@
       <c r="AG549" s="3"/>
       <c r="AH549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -20838,7 +20833,7 @@
       <c r="AG550" s="3"/>
       <c r="AH550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -20874,7 +20869,7 @@
       <c r="AG551" s="3"/>
       <c r="AH551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -20910,7 +20905,7 @@
       <c r="AG552" s="3"/>
       <c r="AH552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -20946,7 +20941,7 @@
       <c r="AG553" s="3"/>
       <c r="AH553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -20982,7 +20977,7 @@
       <c r="AG554" s="3"/>
       <c r="AH554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -21018,7 +21013,7 @@
       <c r="AG555" s="3"/>
       <c r="AH555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -21054,7 +21049,7 @@
       <c r="AG556" s="3"/>
       <c r="AH556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -21090,7 +21085,7 @@
       <c r="AG557" s="3"/>
       <c r="AH557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -21126,7 +21121,7 @@
       <c r="AG558" s="3"/>
       <c r="AH558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -21162,7 +21157,7 @@
       <c r="AG559" s="3"/>
       <c r="AH559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -21198,7 +21193,7 @@
       <c r="AG560" s="3"/>
       <c r="AH560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -21234,7 +21229,7 @@
       <c r="AG561" s="3"/>
       <c r="AH561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -21270,7 +21265,7 @@
       <c r="AG562" s="3"/>
       <c r="AH562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -21306,7 +21301,7 @@
       <c r="AG563" s="3"/>
       <c r="AH563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -21342,7 +21337,7 @@
       <c r="AG564" s="3"/>
       <c r="AH564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -21378,7 +21373,7 @@
       <c r="AG565" s="3"/>
       <c r="AH565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -21414,7 +21409,7 @@
       <c r="AG566" s="3"/>
       <c r="AH566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -21450,7 +21445,7 @@
       <c r="AG567" s="3"/>
       <c r="AH567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -21486,7 +21481,7 @@
       <c r="AG568" s="3"/>
       <c r="AH568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -21522,7 +21517,7 @@
       <c r="AG569" s="3"/>
       <c r="AH569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -21558,7 +21553,7 @@
       <c r="AG570" s="3"/>
       <c r="AH570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -21594,7 +21589,7 @@
       <c r="AG571" s="3"/>
       <c r="AH571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -21630,7 +21625,7 @@
       <c r="AG572" s="3"/>
       <c r="AH572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -21666,7 +21661,7 @@
       <c r="AG573" s="3"/>
       <c r="AH573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -21702,7 +21697,7 @@
       <c r="AG574" s="3"/>
       <c r="AH574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -21738,7 +21733,7 @@
       <c r="AG575" s="3"/>
       <c r="AH575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -21774,7 +21769,7 @@
       <c r="AG576" s="3"/>
       <c r="AH576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -21810,7 +21805,7 @@
       <c r="AG577" s="3"/>
       <c r="AH577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -21846,7 +21841,7 @@
       <c r="AG578" s="3"/>
       <c r="AH578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -21882,7 +21877,7 @@
       <c r="AG579" s="3"/>
       <c r="AH579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -21918,7 +21913,7 @@
       <c r="AG580" s="3"/>
       <c r="AH580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -21954,7 +21949,7 @@
       <c r="AG581" s="3"/>
       <c r="AH581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -21990,7 +21985,7 @@
       <c r="AG582" s="3"/>
       <c r="AH582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -22026,7 +22021,7 @@
       <c r="AG583" s="3"/>
       <c r="AH583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -22062,7 +22057,7 @@
       <c r="AG584" s="3"/>
       <c r="AH584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -22098,7 +22093,7 @@
       <c r="AG585" s="3"/>
       <c r="AH585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -22134,7 +22129,7 @@
       <c r="AG586" s="3"/>
       <c r="AH586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -22170,7 +22165,7 @@
       <c r="AG587" s="3"/>
       <c r="AH587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -22206,7 +22201,7 @@
       <c r="AG588" s="3"/>
       <c r="AH588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -22242,7 +22237,7 @@
       <c r="AG589" s="3"/>
       <c r="AH589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -22278,7 +22273,7 @@
       <c r="AG590" s="3"/>
       <c r="AH590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -22314,7 +22309,7 @@
       <c r="AG591" s="3"/>
       <c r="AH591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -22350,7 +22345,7 @@
       <c r="AG592" s="3"/>
       <c r="AH592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -22386,7 +22381,7 @@
       <c r="AG593" s="3"/>
       <c r="AH593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -22422,7 +22417,7 @@
       <c r="AG594" s="3"/>
       <c r="AH594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -22458,7 +22453,7 @@
       <c r="AG595" s="3"/>
       <c r="AH595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -22494,7 +22489,7 @@
       <c r="AG596" s="3"/>
       <c r="AH596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -22530,7 +22525,7 @@
       <c r="AG597" s="3"/>
       <c r="AH597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -22566,7 +22561,7 @@
       <c r="AG598" s="3"/>
       <c r="AH598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -22602,7 +22597,7 @@
       <c r="AG599" s="3"/>
       <c r="AH599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -22638,7 +22633,7 @@
       <c r="AG600" s="3"/>
       <c r="AH600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -22674,7 +22669,7 @@
       <c r="AG601" s="3"/>
       <c r="AH601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -22710,7 +22705,7 @@
       <c r="AG602" s="3"/>
       <c r="AH602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -22746,7 +22741,7 @@
       <c r="AG603" s="3"/>
       <c r="AH603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -22782,7 +22777,7 @@
       <c r="AG604" s="3"/>
       <c r="AH604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -22818,7 +22813,7 @@
       <c r="AG605" s="3"/>
       <c r="AH605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -22854,7 +22849,7 @@
       <c r="AG606" s="3"/>
       <c r="AH606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -22890,7 +22885,7 @@
       <c r="AG607" s="3"/>
       <c r="AH607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -22926,7 +22921,7 @@
       <c r="AG608" s="3"/>
       <c r="AH608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -22962,7 +22957,7 @@
       <c r="AG609" s="3"/>
       <c r="AH609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -22998,7 +22993,7 @@
       <c r="AG610" s="3"/>
       <c r="AH610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -23034,7 +23029,7 @@
       <c r="AG611" s="3"/>
       <c r="AH611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -23070,7 +23065,7 @@
       <c r="AG612" s="3"/>
       <c r="AH612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -23106,7 +23101,7 @@
       <c r="AG613" s="3"/>
       <c r="AH613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -23142,7 +23137,7 @@
       <c r="AG614" s="3"/>
       <c r="AH614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -23178,7 +23173,7 @@
       <c r="AG615" s="3"/>
       <c r="AH615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -23214,7 +23209,7 @@
       <c r="AG616" s="3"/>
       <c r="AH616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -23250,7 +23245,7 @@
       <c r="AG617" s="3"/>
       <c r="AH617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -23286,7 +23281,7 @@
       <c r="AG618" s="3"/>
       <c r="AH618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -23322,7 +23317,7 @@
       <c r="AG619" s="3"/>
       <c r="AH619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -23358,7 +23353,7 @@
       <c r="AG620" s="3"/>
       <c r="AH620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -23394,7 +23389,7 @@
       <c r="AG621" s="3"/>
       <c r="AH621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -23430,7 +23425,7 @@
       <c r="AG622" s="3"/>
       <c r="AH622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -23466,7 +23461,7 @@
       <c r="AG623" s="3"/>
       <c r="AH623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -23502,7 +23497,7 @@
       <c r="AG624" s="3"/>
       <c r="AH624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -23538,7 +23533,7 @@
       <c r="AG625" s="3"/>
       <c r="AH625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -23574,7 +23569,7 @@
       <c r="AG626" s="3"/>
       <c r="AH626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -23610,7 +23605,7 @@
       <c r="AG627" s="3"/>
       <c r="AH627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -23646,7 +23641,7 @@
       <c r="AG628" s="3"/>
       <c r="AH628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -23682,7 +23677,7 @@
       <c r="AG629" s="3"/>
       <c r="AH629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -23718,7 +23713,7 @@
       <c r="AG630" s="3"/>
       <c r="AH630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -23754,7 +23749,7 @@
       <c r="AG631" s="3"/>
       <c r="AH631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -23790,7 +23785,7 @@
       <c r="AG632" s="3"/>
       <c r="AH632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -23826,7 +23821,7 @@
       <c r="AG633" s="3"/>
       <c r="AH633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -23862,7 +23857,7 @@
       <c r="AG634" s="3"/>
       <c r="AH634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -23898,7 +23893,7 @@
       <c r="AG635" s="3"/>
       <c r="AH635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -23934,7 +23929,7 @@
       <c r="AG636" s="3"/>
       <c r="AH636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -23970,7 +23965,7 @@
       <c r="AG637" s="3"/>
       <c r="AH637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -24006,7 +24001,7 @@
       <c r="AG638" s="3"/>
       <c r="AH638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -24042,7 +24037,7 @@
       <c r="AG639" s="3"/>
       <c r="AH639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -24078,7 +24073,7 @@
       <c r="AG640" s="3"/>
       <c r="AH640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -24114,7 +24109,7 @@
       <c r="AG641" s="3"/>
       <c r="AH641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -24150,7 +24145,7 @@
       <c r="AG642" s="3"/>
       <c r="AH642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -24186,7 +24181,7 @@
       <c r="AG643" s="3"/>
       <c r="AH643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -24222,7 +24217,7 @@
       <c r="AG644" s="3"/>
       <c r="AH644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -24258,7 +24253,7 @@
       <c r="AG645" s="3"/>
       <c r="AH645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -24294,7 +24289,7 @@
       <c r="AG646" s="3"/>
       <c r="AH646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -24330,7 +24325,7 @@
       <c r="AG647" s="3"/>
       <c r="AH647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -24366,7 +24361,7 @@
       <c r="AG648" s="3"/>
       <c r="AH648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -24402,7 +24397,7 @@
       <c r="AG649" s="3"/>
       <c r="AH649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -24438,7 +24433,7 @@
       <c r="AG650" s="3"/>
       <c r="AH650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -24474,7 +24469,7 @@
       <c r="AG651" s="3"/>
       <c r="AH651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -24510,7 +24505,7 @@
       <c r="AG652" s="3"/>
       <c r="AH652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -24546,7 +24541,7 @@
       <c r="AG653" s="3"/>
       <c r="AH653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -24582,7 +24577,7 @@
       <c r="AG654" s="3"/>
       <c r="AH654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -24618,7 +24613,7 @@
       <c r="AG655" s="3"/>
       <c r="AH655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -24654,7 +24649,7 @@
       <c r="AG656" s="3"/>
       <c r="AH656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -24690,7 +24685,7 @@
       <c r="AG657" s="3"/>
       <c r="AH657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -24726,7 +24721,7 @@
       <c r="AG658" s="3"/>
       <c r="AH658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -24762,7 +24757,7 @@
       <c r="AG659" s="3"/>
       <c r="AH659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -24798,7 +24793,7 @@
       <c r="AG660" s="3"/>
       <c r="AH660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -24834,7 +24829,7 @@
       <c r="AG661" s="3"/>
       <c r="AH661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -24870,7 +24865,7 @@
       <c r="AG662" s="3"/>
       <c r="AH662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -24906,7 +24901,7 @@
       <c r="AG663" s="3"/>
       <c r="AH663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -24942,7 +24937,7 @@
       <c r="AG664" s="3"/>
       <c r="AH664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -24978,7 +24973,7 @@
       <c r="AG665" s="3"/>
       <c r="AH665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -25014,7 +25009,7 @@
       <c r="AG666" s="3"/>
       <c r="AH666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -25050,7 +25045,7 @@
       <c r="AG667" s="3"/>
       <c r="AH667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -25086,7 +25081,7 @@
       <c r="AG668" s="3"/>
       <c r="AH668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -25122,7 +25117,7 @@
       <c r="AG669" s="3"/>
       <c r="AH669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -25158,7 +25153,7 @@
       <c r="AG670" s="3"/>
       <c r="AH670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -25194,7 +25189,7 @@
       <c r="AG671" s="3"/>
       <c r="AH671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -25230,7 +25225,7 @@
       <c r="AG672" s="3"/>
       <c r="AH672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -25266,7 +25261,7 @@
       <c r="AG673" s="3"/>
       <c r="AH673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -25302,7 +25297,7 @@
       <c r="AG674" s="3"/>
       <c r="AH674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -25338,7 +25333,7 @@
       <c r="AG675" s="3"/>
       <c r="AH675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -25374,7 +25369,7 @@
       <c r="AG676" s="3"/>
       <c r="AH676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -25410,7 +25405,7 @@
       <c r="AG677" s="3"/>
       <c r="AH677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -25446,7 +25441,7 @@
       <c r="AG678" s="3"/>
       <c r="AH678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -25482,7 +25477,7 @@
       <c r="AG679" s="3"/>
       <c r="AH679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -25518,7 +25513,7 @@
       <c r="AG680" s="3"/>
       <c r="AH680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -25554,7 +25549,7 @@
       <c r="AG681" s="3"/>
       <c r="AH681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -25590,7 +25585,7 @@
       <c r="AG682" s="3"/>
       <c r="AH682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -25626,7 +25621,7 @@
       <c r="AG683" s="3"/>
       <c r="AH683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -25662,7 +25657,7 @@
       <c r="AG684" s="3"/>
       <c r="AH684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -25698,7 +25693,7 @@
       <c r="AG685" s="3"/>
       <c r="AH685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -25734,7 +25729,7 @@
       <c r="AG686" s="3"/>
       <c r="AH686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -25770,7 +25765,7 @@
       <c r="AG687" s="3"/>
       <c r="AH687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -25806,7 +25801,7 @@
       <c r="AG688" s="3"/>
       <c r="AH688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -25842,7 +25837,7 @@
       <c r="AG689" s="3"/>
       <c r="AH689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -25878,7 +25873,7 @@
       <c r="AG690" s="3"/>
       <c r="AH690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -25914,7 +25909,7 @@
       <c r="AG691" s="3"/>
       <c r="AH691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -25950,7 +25945,7 @@
       <c r="AG692" s="3"/>
       <c r="AH692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -25986,7 +25981,7 @@
       <c r="AG693" s="3"/>
       <c r="AH693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -26022,7 +26017,7 @@
       <c r="AG694" s="3"/>
       <c r="AH694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -26058,7 +26053,7 @@
       <c r="AG695" s="3"/>
       <c r="AH695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -26094,7 +26089,7 @@
       <c r="AG696" s="3"/>
       <c r="AH696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -26130,7 +26125,7 @@
       <c r="AG697" s="3"/>
       <c r="AH697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -26166,7 +26161,7 @@
       <c r="AG698" s="3"/>
       <c r="AH698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -26202,7 +26197,7 @@
       <c r="AG699" s="3"/>
       <c r="AH699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -26238,7 +26233,7 @@
       <c r="AG700" s="3"/>
       <c r="AH700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -26274,7 +26269,7 @@
       <c r="AG701" s="3"/>
       <c r="AH701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -26310,7 +26305,7 @@
       <c r="AG702" s="3"/>
       <c r="AH702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -26346,7 +26341,7 @@
       <c r="AG703" s="3"/>
       <c r="AH703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -26382,7 +26377,7 @@
       <c r="AG704" s="3"/>
       <c r="AH704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -26418,7 +26413,7 @@
       <c r="AG705" s="3"/>
       <c r="AH705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -26454,7 +26449,7 @@
       <c r="AG706" s="3"/>
       <c r="AH706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -26490,7 +26485,7 @@
       <c r="AG707" s="3"/>
       <c r="AH707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -26526,7 +26521,7 @@
       <c r="AG708" s="3"/>
       <c r="AH708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -26562,7 +26557,7 @@
       <c r="AG709" s="3"/>
       <c r="AH709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -26598,7 +26593,7 @@
       <c r="AG710" s="3"/>
       <c r="AH710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -26634,7 +26629,7 @@
       <c r="AG711" s="3"/>
       <c r="AH711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -26670,7 +26665,7 @@
       <c r="AG712" s="3"/>
       <c r="AH712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -26706,7 +26701,7 @@
       <c r="AG713" s="3"/>
       <c r="AH713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -26742,7 +26737,7 @@
       <c r="AG714" s="3"/>
       <c r="AH714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -26778,7 +26773,7 @@
       <c r="AG715" s="3"/>
       <c r="AH715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -26814,7 +26809,7 @@
       <c r="AG716" s="3"/>
       <c r="AH716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -26850,7 +26845,7 @@
       <c r="AG717" s="3"/>
       <c r="AH717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -26886,7 +26881,7 @@
       <c r="AG718" s="3"/>
       <c r="AH718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -26922,7 +26917,7 @@
       <c r="AG719" s="3"/>
       <c r="AH719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -26958,7 +26953,7 @@
       <c r="AG720" s="3"/>
       <c r="AH720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -26994,7 +26989,7 @@
       <c r="AG721" s="3"/>
       <c r="AH721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -27030,7 +27025,7 @@
       <c r="AG722" s="3"/>
       <c r="AH722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -27066,7 +27061,7 @@
       <c r="AG723" s="3"/>
       <c r="AH723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -27102,7 +27097,7 @@
       <c r="AG724" s="3"/>
       <c r="AH724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -27138,7 +27133,7 @@
       <c r="AG725" s="3"/>
       <c r="AH725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -27174,7 +27169,7 @@
       <c r="AG726" s="3"/>
       <c r="AH726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -27210,7 +27205,7 @@
       <c r="AG727" s="3"/>
       <c r="AH727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -27246,7 +27241,7 @@
       <c r="AG728" s="3"/>
       <c r="AH728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -27282,7 +27277,7 @@
       <c r="AG729" s="3"/>
       <c r="AH729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -27318,7 +27313,7 @@
       <c r="AG730" s="3"/>
       <c r="AH730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -27354,7 +27349,7 @@
       <c r="AG731" s="3"/>
       <c r="AH731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -27390,7 +27385,7 @@
       <c r="AG732" s="3"/>
       <c r="AH732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -27426,7 +27421,7 @@
       <c r="AG733" s="3"/>
       <c r="AH733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -27462,7 +27457,7 @@
       <c r="AG734" s="3"/>
       <c r="AH734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -27498,7 +27493,7 @@
       <c r="AG735" s="3"/>
       <c r="AH735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -27534,7 +27529,7 @@
       <c r="AG736" s="3"/>
       <c r="AH736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -27570,7 +27565,7 @@
       <c r="AG737" s="3"/>
       <c r="AH737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -27606,7 +27601,7 @@
       <c r="AG738" s="3"/>
       <c r="AH738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -27642,7 +27637,7 @@
       <c r="AG739" s="3"/>
       <c r="AH739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -27678,7 +27673,7 @@
       <c r="AG740" s="3"/>
       <c r="AH740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -27714,7 +27709,7 @@
       <c r="AG741" s="3"/>
       <c r="AH741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -27750,7 +27745,7 @@
       <c r="AG742" s="3"/>
       <c r="AH742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -27786,7 +27781,7 @@
       <c r="AG743" s="3"/>
       <c r="AH743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -27822,7 +27817,7 @@
       <c r="AG744" s="3"/>
       <c r="AH744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -27858,7 +27853,7 @@
       <c r="AG745" s="3"/>
       <c r="AH745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -27894,7 +27889,7 @@
       <c r="AG746" s="3"/>
       <c r="AH746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -27930,7 +27925,7 @@
       <c r="AG747" s="3"/>
       <c r="AH747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -27966,7 +27961,7 @@
       <c r="AG748" s="3"/>
       <c r="AH748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -28002,7 +27997,7 @@
       <c r="AG749" s="3"/>
       <c r="AH749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -28038,7 +28033,7 @@
       <c r="AG750" s="3"/>
       <c r="AH750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -28074,7 +28069,7 @@
       <c r="AG751" s="3"/>
       <c r="AH751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -28110,7 +28105,7 @@
       <c r="AG752" s="3"/>
       <c r="AH752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -28146,7 +28141,7 @@
       <c r="AG753" s="3"/>
       <c r="AH753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -28182,7 +28177,7 @@
       <c r="AG754" s="3"/>
       <c r="AH754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -28218,7 +28213,7 @@
       <c r="AG755" s="3"/>
       <c r="AH755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -28254,7 +28249,7 @@
       <c r="AG756" s="3"/>
       <c r="AH756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -28290,7 +28285,7 @@
       <c r="AG757" s="3"/>
       <c r="AH757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -28326,7 +28321,7 @@
       <c r="AG758" s="3"/>
       <c r="AH758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -28362,7 +28357,7 @@
       <c r="AG759" s="3"/>
       <c r="AH759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -28398,7 +28393,7 @@
       <c r="AG760" s="3"/>
       <c r="AH760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -28434,7 +28429,7 @@
       <c r="AG761" s="3"/>
       <c r="AH761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -28470,7 +28465,7 @@
       <c r="AG762" s="3"/>
       <c r="AH762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -28506,7 +28501,7 @@
       <c r="AG763" s="3"/>
       <c r="AH763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -28542,7 +28537,7 @@
       <c r="AG764" s="3"/>
       <c r="AH764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -28578,7 +28573,7 @@
       <c r="AG765" s="3"/>
       <c r="AH765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -28614,7 +28609,7 @@
       <c r="AG766" s="3"/>
       <c r="AH766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -28650,7 +28645,7 @@
       <c r="AG767" s="3"/>
       <c r="AH767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -28686,7 +28681,7 @@
       <c r="AG768" s="3"/>
       <c r="AH768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -28722,7 +28717,7 @@
       <c r="AG769" s="3"/>
       <c r="AH769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -28758,7 +28753,7 @@
       <c r="AG770" s="3"/>
       <c r="AH770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -28794,7 +28789,7 @@
       <c r="AG771" s="3"/>
       <c r="AH771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -28830,7 +28825,7 @@
       <c r="AG772" s="3"/>
       <c r="AH772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -28866,7 +28861,7 @@
       <c r="AG773" s="3"/>
       <c r="AH773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -28902,7 +28897,7 @@
       <c r="AG774" s="3"/>
       <c r="AH774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -28938,7 +28933,7 @@
       <c r="AG775" s="3"/>
       <c r="AH775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -28974,7 +28969,7 @@
       <c r="AG776" s="3"/>
       <c r="AH776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -29010,7 +29005,7 @@
       <c r="AG777" s="3"/>
       <c r="AH777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -29046,7 +29041,7 @@
       <c r="AG778" s="3"/>
       <c r="AH778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -29082,7 +29077,7 @@
       <c r="AG779" s="3"/>
       <c r="AH779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -29118,7 +29113,7 @@
       <c r="AG780" s="3"/>
       <c r="AH780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -29154,7 +29149,7 @@
       <c r="AG781" s="3"/>
       <c r="AH781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -29190,7 +29185,7 @@
       <c r="AG782" s="3"/>
       <c r="AH782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -29226,7 +29221,7 @@
       <c r="AG783" s="3"/>
       <c r="AH783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -29262,7 +29257,7 @@
       <c r="AG784" s="3"/>
       <c r="AH784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -29298,7 +29293,7 @@
       <c r="AG785" s="3"/>
       <c r="AH785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -29334,7 +29329,7 @@
       <c r="AG786" s="3"/>
       <c r="AH786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -29370,7 +29365,7 @@
       <c r="AG787" s="3"/>
       <c r="AH787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -29406,7 +29401,7 @@
       <c r="AG788" s="3"/>
       <c r="AH788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -29442,7 +29437,7 @@
       <c r="AG789" s="3"/>
       <c r="AH789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -29478,7 +29473,7 @@
       <c r="AG790" s="3"/>
       <c r="AH790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -29514,7 +29509,7 @@
       <c r="AG791" s="3"/>
       <c r="AH791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -29550,7 +29545,7 @@
       <c r="AG792" s="3"/>
       <c r="AH792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -29586,7 +29581,7 @@
       <c r="AG793" s="3"/>
       <c r="AH793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -29622,7 +29617,7 @@
       <c r="AG794" s="3"/>
       <c r="AH794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -29658,7 +29653,7 @@
       <c r="AG795" s="3"/>
       <c r="AH795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -29694,7 +29689,7 @@
       <c r="AG796" s="3"/>
       <c r="AH796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -29730,7 +29725,7 @@
       <c r="AG797" s="3"/>
       <c r="AH797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -29766,7 +29761,7 @@
       <c r="AG798" s="3"/>
       <c r="AH798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -29802,7 +29797,7 @@
       <c r="AG799" s="3"/>
       <c r="AH799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -29838,7 +29833,7 @@
       <c r="AG800" s="3"/>
       <c r="AH800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -29874,7 +29869,7 @@
       <c r="AG801" s="3"/>
       <c r="AH801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -29910,7 +29905,7 @@
       <c r="AG802" s="3"/>
       <c r="AH802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -29946,7 +29941,7 @@
       <c r="AG803" s="3"/>
       <c r="AH803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -29982,7 +29977,7 @@
       <c r="AG804" s="3"/>
       <c r="AH804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -30018,7 +30013,7 @@
       <c r="AG805" s="3"/>
       <c r="AH805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -30054,7 +30049,7 @@
       <c r="AG806" s="3"/>
       <c r="AH806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -30090,7 +30085,7 @@
       <c r="AG807" s="3"/>
       <c r="AH807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -30126,7 +30121,7 @@
       <c r="AG808" s="3"/>
       <c r="AH808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -30162,7 +30157,7 @@
       <c r="AG809" s="3"/>
       <c r="AH809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -30198,7 +30193,7 @@
       <c r="AG810" s="3"/>
       <c r="AH810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -30234,7 +30229,7 @@
       <c r="AG811" s="3"/>
       <c r="AH811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -30270,7 +30265,7 @@
       <c r="AG812" s="3"/>
       <c r="AH812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -30306,7 +30301,7 @@
       <c r="AG813" s="3"/>
       <c r="AH813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -30342,7 +30337,7 @@
       <c r="AG814" s="3"/>
       <c r="AH814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -30378,7 +30373,7 @@
       <c r="AG815" s="3"/>
       <c r="AH815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -30414,7 +30409,7 @@
       <c r="AG816" s="3"/>
       <c r="AH816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -30450,7 +30445,7 @@
       <c r="AG817" s="3"/>
       <c r="AH817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -30486,7 +30481,7 @@
       <c r="AG818" s="3"/>
       <c r="AH818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -30522,7 +30517,7 @@
       <c r="AG819" s="3"/>
       <c r="AH819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -30558,7 +30553,7 @@
       <c r="AG820" s="3"/>
       <c r="AH820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -30594,7 +30589,7 @@
       <c r="AG821" s="3"/>
       <c r="AH821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -30630,7 +30625,7 @@
       <c r="AG822" s="3"/>
       <c r="AH822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -30666,7 +30661,7 @@
       <c r="AG823" s="3"/>
       <c r="AH823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -30702,7 +30697,7 @@
       <c r="AG824" s="3"/>
       <c r="AH824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -30738,7 +30733,7 @@
       <c r="AG825" s="3"/>
       <c r="AH825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -30774,7 +30769,7 @@
       <c r="AG826" s="3"/>
       <c r="AH826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -30810,7 +30805,7 @@
       <c r="AG827" s="3"/>
       <c r="AH827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -30846,7 +30841,7 @@
       <c r="AG828" s="3"/>
       <c r="AH828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -30882,7 +30877,7 @@
       <c r="AG829" s="3"/>
       <c r="AH829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -30918,7 +30913,7 @@
       <c r="AG830" s="3"/>
       <c r="AH830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -30954,7 +30949,7 @@
       <c r="AG831" s="3"/>
       <c r="AH831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -30990,7 +30985,7 @@
       <c r="AG832" s="3"/>
       <c r="AH832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -31026,7 +31021,7 @@
       <c r="AG833" s="3"/>
       <c r="AH833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -31062,7 +31057,7 @@
       <c r="AG834" s="3"/>
       <c r="AH834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -31098,7 +31093,7 @@
       <c r="AG835" s="3"/>
       <c r="AH835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -31134,7 +31129,7 @@
       <c r="AG836" s="3"/>
       <c r="AH836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -31170,7 +31165,7 @@
       <c r="AG837" s="3"/>
       <c r="AH837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -31206,7 +31201,7 @@
       <c r="AG838" s="3"/>
       <c r="AH838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -31242,7 +31237,7 @@
       <c r="AG839" s="3"/>
       <c r="AH839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -31278,7 +31273,7 @@
       <c r="AG840" s="3"/>
       <c r="AH840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -31314,7 +31309,7 @@
       <c r="AG841" s="3"/>
       <c r="AH841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -31350,7 +31345,7 @@
       <c r="AG842" s="3"/>
       <c r="AH842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -31386,7 +31381,7 @@
       <c r="AG843" s="3"/>
       <c r="AH843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -31422,7 +31417,7 @@
       <c r="AG844" s="3"/>
       <c r="AH844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -31458,7 +31453,7 @@
       <c r="AG845" s="3"/>
       <c r="AH845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -31494,7 +31489,7 @@
       <c r="AG846" s="3"/>
       <c r="AH846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -31530,7 +31525,7 @@
       <c r="AG847" s="3"/>
       <c r="AH847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -31566,7 +31561,7 @@
       <c r="AG848" s="3"/>
       <c r="AH848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -31602,7 +31597,7 @@
       <c r="AG849" s="3"/>
       <c r="AH849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -31638,7 +31633,7 @@
       <c r="AG850" s="3"/>
       <c r="AH850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -31674,7 +31669,7 @@
       <c r="AG851" s="3"/>
       <c r="AH851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -31710,7 +31705,7 @@
       <c r="AG852" s="3"/>
       <c r="AH852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -31746,7 +31741,7 @@
       <c r="AG853" s="3"/>
       <c r="AH853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -31782,7 +31777,7 @@
       <c r="AG854" s="3"/>
       <c r="AH854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -31818,7 +31813,7 @@
       <c r="AG855" s="3"/>
       <c r="AH855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -31854,7 +31849,7 @@
       <c r="AG856" s="3"/>
       <c r="AH856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -31890,7 +31885,7 @@
       <c r="AG857" s="3"/>
       <c r="AH857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -31926,7 +31921,7 @@
       <c r="AG858" s="3"/>
       <c r="AH858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -31962,7 +31957,7 @@
       <c r="AG859" s="3"/>
       <c r="AH859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -31998,7 +31993,7 @@
       <c r="AG860" s="3"/>
       <c r="AH860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -32034,7 +32029,7 @@
       <c r="AG861" s="3"/>
       <c r="AH861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -32070,7 +32065,7 @@
       <c r="AG862" s="3"/>
       <c r="AH862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -32106,7 +32101,7 @@
       <c r="AG863" s="3"/>
       <c r="AH863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -32142,7 +32137,7 @@
       <c r="AG864" s="3"/>
       <c r="AH864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -32178,7 +32173,7 @@
       <c r="AG865" s="3"/>
       <c r="AH865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -32214,7 +32209,7 @@
       <c r="AG866" s="3"/>
       <c r="AH866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -32250,7 +32245,7 @@
       <c r="AG867" s="3"/>
       <c r="AH867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -32286,7 +32281,7 @@
       <c r="AG868" s="3"/>
       <c r="AH868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -32322,7 +32317,7 @@
       <c r="AG869" s="3"/>
       <c r="AH869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -32358,7 +32353,7 @@
       <c r="AG870" s="3"/>
       <c r="AH870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -32394,7 +32389,7 @@
       <c r="AG871" s="3"/>
       <c r="AH871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -32430,7 +32425,7 @@
       <c r="AG872" s="3"/>
       <c r="AH872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -32466,7 +32461,7 @@
       <c r="AG873" s="3"/>
       <c r="AH873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -32502,7 +32497,7 @@
       <c r="AG874" s="3"/>
       <c r="AH874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -32538,7 +32533,7 @@
       <c r="AG875" s="3"/>
       <c r="AH875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -32574,7 +32569,7 @@
       <c r="AG876" s="3"/>
       <c r="AH876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -32610,7 +32605,7 @@
       <c r="AG877" s="3"/>
       <c r="AH877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -32646,7 +32641,7 @@
       <c r="AG878" s="3"/>
       <c r="AH878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -32682,7 +32677,7 @@
       <c r="AG879" s="3"/>
       <c r="AH879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -32718,7 +32713,7 @@
       <c r="AG880" s="3"/>
       <c r="AH880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -32754,7 +32749,7 @@
       <c r="AG881" s="3"/>
       <c r="AH881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -32790,7 +32785,7 @@
       <c r="AG882" s="3"/>
       <c r="AH882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -32826,7 +32821,7 @@
       <c r="AG883" s="3"/>
       <c r="AH883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -32862,7 +32857,7 @@
       <c r="AG884" s="3"/>
       <c r="AH884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -32898,7 +32893,7 @@
       <c r="AG885" s="3"/>
       <c r="AH885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -32934,7 +32929,7 @@
       <c r="AG886" s="3"/>
       <c r="AH886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -32970,7 +32965,7 @@
       <c r="AG887" s="3"/>
       <c r="AH887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -33006,7 +33001,7 @@
       <c r="AG888" s="3"/>
       <c r="AH888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -33042,7 +33037,7 @@
       <c r="AG889" s="3"/>
       <c r="AH889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -33078,7 +33073,7 @@
       <c r="AG890" s="3"/>
       <c r="AH890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -33114,7 +33109,7 @@
       <c r="AG891" s="3"/>
       <c r="AH891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -33150,7 +33145,7 @@
       <c r="AG892" s="3"/>
       <c r="AH892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -33186,7 +33181,7 @@
       <c r="AG893" s="3"/>
       <c r="AH893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -33222,7 +33217,7 @@
       <c r="AG894" s="3"/>
       <c r="AH894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -33258,7 +33253,7 @@
       <c r="AG895" s="3"/>
       <c r="AH895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -33294,7 +33289,7 @@
       <c r="AG896" s="3"/>
       <c r="AH896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -33330,7 +33325,7 @@
       <c r="AG897" s="3"/>
       <c r="AH897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -33366,7 +33361,7 @@
       <c r="AG898" s="3"/>
       <c r="AH898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -33402,7 +33397,7 @@
       <c r="AG899" s="3"/>
       <c r="AH899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -33438,7 +33433,7 @@
       <c r="AG900" s="3"/>
       <c r="AH900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -33474,7 +33469,7 @@
       <c r="AG901" s="3"/>
       <c r="AH901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -33510,7 +33505,7 @@
       <c r="AG902" s="3"/>
       <c r="AH902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -33546,7 +33541,7 @@
       <c r="AG903" s="3"/>
       <c r="AH903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -33582,7 +33577,7 @@
       <c r="AG904" s="3"/>
       <c r="AH904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -33618,7 +33613,7 @@
       <c r="AG905" s="3"/>
       <c r="AH905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -33654,7 +33649,7 @@
       <c r="AG906" s="3"/>
       <c r="AH906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -33690,7 +33685,7 @@
       <c r="AG907" s="3"/>
       <c r="AH907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -33726,7 +33721,7 @@
       <c r="AG908" s="3"/>
       <c r="AH908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -33762,7 +33757,7 @@
       <c r="AG909" s="3"/>
       <c r="AH909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -33798,7 +33793,7 @@
       <c r="AG910" s="3"/>
       <c r="AH910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -33834,7 +33829,7 @@
       <c r="AG911" s="3"/>
       <c r="AH911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -33870,7 +33865,7 @@
       <c r="AG912" s="3"/>
       <c r="AH912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -33906,7 +33901,7 @@
       <c r="AG913" s="3"/>
       <c r="AH913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -33942,7 +33937,7 @@
       <c r="AG914" s="3"/>
       <c r="AH914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -33978,7 +33973,7 @@
       <c r="AG915" s="3"/>
       <c r="AH915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -34014,7 +34009,7 @@
       <c r="AG916" s="3"/>
       <c r="AH916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -34050,7 +34045,7 @@
       <c r="AG917" s="3"/>
       <c r="AH917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -34086,7 +34081,7 @@
       <c r="AG918" s="3"/>
       <c r="AH918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -34122,7 +34117,7 @@
       <c r="AG919" s="3"/>
       <c r="AH919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -34158,7 +34153,7 @@
       <c r="AG920" s="3"/>
       <c r="AH920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -34194,7 +34189,7 @@
       <c r="AG921" s="3"/>
       <c r="AH921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -34230,7 +34225,7 @@
       <c r="AG922" s="3"/>
       <c r="AH922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -34266,7 +34261,7 @@
       <c r="AG923" s="3"/>
       <c r="AH923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -34302,7 +34297,7 @@
       <c r="AG924" s="3"/>
       <c r="AH924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -34338,7 +34333,7 @@
       <c r="AG925" s="3"/>
       <c r="AH925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -34374,7 +34369,7 @@
       <c r="AG926" s="3"/>
       <c r="AH926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -34410,7 +34405,7 @@
       <c r="AG927" s="3"/>
       <c r="AH927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -34446,7 +34441,7 @@
       <c r="AG928" s="3"/>
       <c r="AH928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -34482,7 +34477,7 @@
       <c r="AG929" s="3"/>
       <c r="AH929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -34518,7 +34513,7 @@
       <c r="AG930" s="3"/>
       <c r="AH930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -34554,7 +34549,7 @@
       <c r="AG931" s="3"/>
       <c r="AH931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -34590,7 +34585,7 @@
       <c r="AG932" s="3"/>
       <c r="AH932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -34626,7 +34621,7 @@
       <c r="AG933" s="3"/>
       <c r="AH933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -34662,7 +34657,7 @@
       <c r="AG934" s="3"/>
       <c r="AH934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -34698,7 +34693,7 @@
       <c r="AG935" s="3"/>
       <c r="AH935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -34734,7 +34729,7 @@
       <c r="AG936" s="3"/>
       <c r="AH936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -34770,7 +34765,7 @@
       <c r="AG937" s="3"/>
       <c r="AH937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -34806,7 +34801,7 @@
       <c r="AG938" s="3"/>
       <c r="AH938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -34842,7 +34837,7 @@
       <c r="AG939" s="3"/>
       <c r="AH939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -34878,7 +34873,7 @@
       <c r="AG940" s="3"/>
       <c r="AH940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -34914,7 +34909,7 @@
       <c r="AG941" s="3"/>
       <c r="AH941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -34950,7 +34945,7 @@
       <c r="AG942" s="3"/>
       <c r="AH942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -34986,7 +34981,7 @@
       <c r="AG943" s="3"/>
       <c r="AH943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -35022,7 +35017,7 @@
       <c r="AG944" s="3"/>
       <c r="AH944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -35058,7 +35053,7 @@
       <c r="AG945" s="3"/>
       <c r="AH945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -35094,7 +35089,7 @@
       <c r="AG946" s="3"/>
       <c r="AH946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -35130,7 +35125,7 @@
       <c r="AG947" s="3"/>
       <c r="AH947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -35166,7 +35161,7 @@
       <c r="AG948" s="3"/>
       <c r="AH948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -35202,7 +35197,7 @@
       <c r="AG949" s="3"/>
       <c r="AH949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -35238,7 +35233,7 @@
       <c r="AG950" s="3"/>
       <c r="AH950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -35274,7 +35269,7 @@
       <c r="AG951" s="3"/>
       <c r="AH951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -35310,7 +35305,7 @@
       <c r="AG952" s="3"/>
       <c r="AH952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -35346,7 +35341,7 @@
       <c r="AG953" s="3"/>
       <c r="AH953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -35382,7 +35377,7 @@
       <c r="AG954" s="3"/>
       <c r="AH954" s="3"/>
     </row>
-    <row r="955">
+    <row r="955" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -35418,7 +35413,7 @@
       <c r="AG955" s="3"/>
       <c r="AH955" s="3"/>
     </row>
-    <row r="956">
+    <row r="956" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -35454,7 +35449,7 @@
       <c r="AG956" s="3"/>
       <c r="AH956" s="3"/>
     </row>
-    <row r="957">
+    <row r="957" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -35490,7 +35485,7 @@
       <c r="AG957" s="3"/>
       <c r="AH957" s="3"/>
     </row>
-    <row r="958">
+    <row r="958" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -35526,7 +35521,7 @@
       <c r="AG958" s="3"/>
       <c r="AH958" s="3"/>
     </row>
-    <row r="959">
+    <row r="959" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A959" s="3"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
@@ -35562,7 +35557,7 @@
       <c r="AG959" s="3"/>
       <c r="AH959" s="3"/>
     </row>
-    <row r="960">
+    <row r="960" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A960" s="3"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
@@ -35598,7 +35593,7 @@
       <c r="AG960" s="3"/>
       <c r="AH960" s="3"/>
     </row>
-    <row r="961">
+    <row r="961" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A961" s="3"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
@@ -35634,7 +35629,7 @@
       <c r="AG961" s="3"/>
       <c r="AH961" s="3"/>
     </row>
-    <row r="962">
+    <row r="962" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A962" s="3"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
@@ -35670,7 +35665,7 @@
       <c r="AG962" s="3"/>
       <c r="AH962" s="3"/>
     </row>
-    <row r="963">
+    <row r="963" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A963" s="3"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
@@ -35706,7 +35701,7 @@
       <c r="AG963" s="3"/>
       <c r="AH963" s="3"/>
     </row>
-    <row r="964">
+    <row r="964" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A964" s="3"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
@@ -35742,7 +35737,7 @@
       <c r="AG964" s="3"/>
       <c r="AH964" s="3"/>
     </row>
-    <row r="965">
+    <row r="965" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A965" s="3"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
@@ -35778,7 +35773,7 @@
       <c r="AG965" s="3"/>
       <c r="AH965" s="3"/>
     </row>
-    <row r="966">
+    <row r="966" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A966" s="3"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
@@ -35814,7 +35809,7 @@
       <c r="AG966" s="3"/>
       <c r="AH966" s="3"/>
     </row>
-    <row r="967">
+    <row r="967" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A967" s="3"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
@@ -35850,7 +35845,7 @@
       <c r="AG967" s="3"/>
       <c r="AH967" s="3"/>
     </row>
-    <row r="968">
+    <row r="968" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A968" s="3"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
@@ -35886,7 +35881,7 @@
       <c r="AG968" s="3"/>
       <c r="AH968" s="3"/>
     </row>
-    <row r="969">
+    <row r="969" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A969" s="3"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
@@ -35922,7 +35917,7 @@
       <c r="AG969" s="3"/>
       <c r="AH969" s="3"/>
     </row>
-    <row r="970">
+    <row r="970" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A970" s="3"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
@@ -35958,7 +35953,7 @@
       <c r="AG970" s="3"/>
       <c r="AH970" s="3"/>
     </row>
-    <row r="971">
+    <row r="971" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A971" s="3"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
@@ -35994,7 +35989,7 @@
       <c r="AG971" s="3"/>
       <c r="AH971" s="3"/>
     </row>
-    <row r="972">
+    <row r="972" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A972" s="3"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
@@ -36030,7 +36025,7 @@
       <c r="AG972" s="3"/>
       <c r="AH972" s="3"/>
     </row>
-    <row r="973">
+    <row r="973" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A973" s="3"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
@@ -36066,7 +36061,7 @@
       <c r="AG973" s="3"/>
       <c r="AH973" s="3"/>
     </row>
-    <row r="974">
+    <row r="974" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -36102,7 +36097,7 @@
       <c r="AG974" s="3"/>
       <c r="AH974" s="3"/>
     </row>
-    <row r="975">
+    <row r="975" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A975" s="3"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
@@ -36138,7 +36133,7 @@
       <c r="AG975" s="3"/>
       <c r="AH975" s="3"/>
     </row>
-    <row r="976">
+    <row r="976" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
@@ -36174,7 +36169,7 @@
       <c r="AG976" s="3"/>
       <c r="AH976" s="3"/>
     </row>
-    <row r="977">
+    <row r="977" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -36210,7 +36205,7 @@
       <c r="AG977" s="3"/>
       <c r="AH977" s="3"/>
     </row>
-    <row r="978">
+    <row r="978" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A978" s="3"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
@@ -36246,7 +36241,7 @@
       <c r="AG978" s="3"/>
       <c r="AH978" s="3"/>
     </row>
-    <row r="979">
+    <row r="979" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A979" s="3"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
@@ -36282,7 +36277,7 @@
       <c r="AG979" s="3"/>
       <c r="AH979" s="3"/>
     </row>
-    <row r="980">
+    <row r="980" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A980" s="3"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
@@ -36318,7 +36313,7 @@
       <c r="AG980" s="3"/>
       <c r="AH980" s="3"/>
     </row>
-    <row r="981">
+    <row r="981" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A981" s="3"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
@@ -36354,7 +36349,7 @@
       <c r="AG981" s="3"/>
       <c r="AH981" s="3"/>
     </row>
-    <row r="982">
+    <row r="982" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A982" s="3"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
@@ -36390,7 +36385,7 @@
       <c r="AG982" s="3"/>
       <c r="AH982" s="3"/>
     </row>
-    <row r="983">
+    <row r="983" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A983" s="3"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
@@ -36426,7 +36421,7 @@
       <c r="AG983" s="3"/>
       <c r="AH983" s="3"/>
     </row>
-    <row r="984">
+    <row r="984" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A984" s="3"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
@@ -36462,7 +36457,7 @@
       <c r="AG984" s="3"/>
       <c r="AH984" s="3"/>
     </row>
-    <row r="985">
+    <row r="985" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A985" s="3"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
@@ -36498,7 +36493,7 @@
       <c r="AG985" s="3"/>
       <c r="AH985" s="3"/>
     </row>
-    <row r="986">
+    <row r="986" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A986" s="3"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
@@ -36534,7 +36529,7 @@
       <c r="AG986" s="3"/>
       <c r="AH986" s="3"/>
     </row>
-    <row r="987">
+    <row r="987" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A987" s="3"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
@@ -36570,7 +36565,7 @@
       <c r="AG987" s="3"/>
       <c r="AH987" s="3"/>
     </row>
-    <row r="988">
+    <row r="988" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A988" s="3"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
@@ -36606,7 +36601,7 @@
       <c r="AG988" s="3"/>
       <c r="AH988" s="3"/>
     </row>
-    <row r="989">
+    <row r="989" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
@@ -36642,7 +36637,7 @@
       <c r="AG989" s="3"/>
       <c r="AH989" s="3"/>
     </row>
-    <row r="990">
+    <row r="990" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A990" s="3"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
@@ -36678,7 +36673,7 @@
       <c r="AG990" s="3"/>
       <c r="AH990" s="3"/>
     </row>
-    <row r="991">
+    <row r="991" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A991" s="3"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
@@ -36714,7 +36709,7 @@
       <c r="AG991" s="3"/>
       <c r="AH991" s="3"/>
     </row>
-    <row r="992">
+    <row r="992" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A992" s="3"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
@@ -36750,7 +36745,7 @@
       <c r="AG992" s="3"/>
       <c r="AH992" s="3"/>
     </row>
-    <row r="993">
+    <row r="993" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -36786,7 +36781,7 @@
       <c r="AG993" s="3"/>
       <c r="AH993" s="3"/>
     </row>
-    <row r="994">
+    <row r="994" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -36822,7 +36817,7 @@
       <c r="AG994" s="3"/>
       <c r="AH994" s="3"/>
     </row>
-    <row r="995">
+    <row r="995" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -36858,7 +36853,7 @@
       <c r="AG995" s="3"/>
       <c r="AH995" s="3"/>
     </row>
-    <row r="996">
+    <row r="996" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A996" s="3"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
@@ -36894,7 +36889,7 @@
       <c r="AG996" s="3"/>
       <c r="AH996" s="3"/>
     </row>
-    <row r="997">
+    <row r="997" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A997" s="3"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
@@ -36930,7 +36925,7 @@
       <c r="AG997" s="3"/>
       <c r="AH997" s="3"/>
     </row>
-    <row r="998">
+    <row r="998" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A998" s="3"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
@@ -36966,7 +36961,7 @@
       <c r="AG998" s="3"/>
       <c r="AH998" s="3"/>
     </row>
-    <row r="999">
+    <row r="999" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A999" s="3"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
@@ -37002,7 +36997,7 @@
       <c r="AG999" s="3"/>
       <c r="AH999" s="3"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="1:34" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A1000" s="3"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
@@ -37039,9 +37034,12 @@
       <c r="AH1000" s="3"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A38:I38"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>